--- a/Другое/Кино.xlsx
+++ b/Другое/Кино.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="149">
   <si>
     <t>№</t>
   </si>
@@ -479,8 +479,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -615,6 +615,9 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -649,6 +652,14 @@
       <color rgb="FFF99D41"/>
     </mruColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -695,7 +706,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -727,9 +738,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -761,6 +773,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -936,9 +949,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I122"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="24.85546875" style="1" customWidth="1"/>
@@ -951,7 +964,7 @@
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -980,7 +993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>6</v>
       </c>
@@ -1003,7 +1016,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>7</v>
       </c>
@@ -1026,7 +1039,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>8</v>
       </c>
@@ -1049,7 +1062,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -1072,7 +1085,7 @@
       <c r="H5" s="4"/>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1095,7 +1108,7 @@
       <c r="H6" s="4"/>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>11</v>
       </c>
@@ -1118,7 +1131,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>9</v>
       </c>
@@ -1141,7 +1154,7 @@
       <c r="H8" s="4"/>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>12</v>
       </c>
@@ -1164,7 +1177,7 @@
       <c r="H9" s="4"/>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>15</v>
       </c>
@@ -1187,7 +1200,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>4</v>
       </c>
@@ -1210,7 +1223,7 @@
       <c r="H11" s="4"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>1</v>
       </c>
@@ -1229,11 +1242,17 @@
       <c r="F12" s="7">
         <v>8.1</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="G12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="4">
+        <v>8</v>
+      </c>
+      <c r="I12" s="20">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>13</v>
       </c>
@@ -1256,7 +1275,7 @@
       <c r="H13" s="4"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -1279,7 +1298,7 @@
       <c r="H14" s="4"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -1302,7 +1321,7 @@
       <c r="H15" s="4"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>16</v>
       </c>
@@ -1325,7 +1344,7 @@
       <c r="H16" s="4"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>10</v>
       </c>
@@ -1348,7 +1367,7 @@
       <c r="H17" s="4"/>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -1377,7 +1396,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -1400,7 +1419,7 @@
       <c r="H19" s="4"/>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" ht="29.25">
+    <row r="20" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>36</v>
       </c>
@@ -1429,7 +1448,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -1452,7 +1471,7 @@
       <c r="H21" s="4"/>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="29.25">
+    <row r="22" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>37</v>
       </c>
@@ -1475,7 +1494,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>39</v>
       </c>
@@ -1496,7 +1515,7 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -1525,7 +1544,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>41</v>
       </c>
@@ -1546,7 +1565,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>49</v>
       </c>
@@ -1567,7 +1586,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>40</v>
       </c>
@@ -1588,7 +1607,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>19</v>
       </c>
@@ -1611,7 +1630,7 @@
       <c r="H28" s="4"/>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>22</v>
       </c>
@@ -1640,7 +1659,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>42</v>
       </c>
@@ -1661,7 +1680,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>23</v>
       </c>
@@ -1684,7 +1703,7 @@
       <c r="H31" s="4"/>
       <c r="I31" s="6"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>43</v>
       </c>
@@ -1705,7 +1724,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>75</v>
       </c>
@@ -1726,7 +1745,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>27</v>
       </c>
@@ -1755,7 +1774,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>48</v>
       </c>
@@ -1776,7 +1795,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>44</v>
       </c>
@@ -1797,7 +1816,7 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>24</v>
       </c>
@@ -1820,7 +1839,7 @@
       <c r="H37" s="4"/>
       <c r="I37" s="6"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>25</v>
       </c>
@@ -1849,7 +1868,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -1872,7 +1891,7 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>76</v>
       </c>
@@ -1893,7 +1912,7 @@
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>28</v>
       </c>
@@ -1922,7 +1941,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>80</v>
       </c>
@@ -1943,7 +1962,7 @@
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>51</v>
       </c>
@@ -1970,7 +1989,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>52</v>
       </c>
@@ -1997,7 +2016,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>26</v>
       </c>
@@ -2026,7 +2045,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>70</v>
       </c>
@@ -2053,7 +2072,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>72</v>
       </c>
@@ -2074,7 +2093,7 @@
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46</v>
       </c>
@@ -2095,7 +2114,7 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>53</v>
       </c>
@@ -2122,7 +2141,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>65</v>
       </c>
@@ -2149,7 +2168,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>95</v>
       </c>
@@ -2170,7 +2189,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>74</v>
       </c>
@@ -2197,7 +2216,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>101</v>
       </c>
@@ -2218,7 +2237,7 @@
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>50</v>
       </c>
@@ -2239,7 +2258,7 @@
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>66</v>
       </c>
@@ -2266,7 +2285,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>97</v>
       </c>
@@ -2287,7 +2306,7 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>92</v>
       </c>
@@ -2308,7 +2327,7 @@
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>108</v>
       </c>
@@ -2335,7 +2354,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>47</v>
       </c>
@@ -2362,7 +2381,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>77</v>
       </c>
@@ -2383,7 +2402,7 @@
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
-    <row r="61" spans="1:9" ht="42.75">
+    <row r="61" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>31</v>
       </c>
@@ -2412,7 +2431,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>63</v>
       </c>
@@ -2433,7 +2452,7 @@
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>102</v>
       </c>
@@ -2460,7 +2479,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>54</v>
       </c>
@@ -2481,7 +2500,7 @@
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>89</v>
       </c>
@@ -2502,7 +2521,7 @@
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>29</v>
       </c>
@@ -2531,7 +2550,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>55</v>
       </c>
@@ -2552,7 +2571,7 @@
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>91</v>
       </c>
@@ -2573,7 +2592,7 @@
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>103</v>
       </c>
@@ -2600,7 +2619,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="57">
+    <row r="70" spans="1:9" ht="57" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>30</v>
       </c>
@@ -2629,7 +2648,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>104</v>
       </c>
@@ -2656,7 +2675,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>56</v>
       </c>
@@ -2677,7 +2696,7 @@
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>71</v>
       </c>
@@ -2704,7 +2723,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -2731,7 +2750,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>94</v>
       </c>
@@ -2758,7 +2777,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="29.25">
+    <row r="76" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>62</v>
       </c>
@@ -2785,7 +2804,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>78</v>
       </c>
@@ -2806,7 +2825,7 @@
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>111</v>
       </c>
@@ -2833,7 +2852,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>33</v>
       </c>
@@ -2862,7 +2881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>57</v>
       </c>
@@ -2889,7 +2908,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>58</v>
       </c>
@@ -2916,7 +2935,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>69</v>
       </c>
@@ -2937,7 +2956,7 @@
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>79</v>
       </c>
@@ -2958,7 +2977,7 @@
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>82</v>
       </c>
@@ -2979,7 +2998,7 @@
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>109</v>
       </c>
@@ -3006,7 +3025,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>67</v>
       </c>
@@ -3027,7 +3046,7 @@
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>99</v>
       </c>
@@ -3048,7 +3067,7 @@
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>107</v>
       </c>
@@ -3075,7 +3094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="42.75">
+    <row r="89" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>32</v>
       </c>
@@ -3104,7 +3123,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>81</v>
       </c>
@@ -3125,7 +3144,7 @@
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>68</v>
       </c>
@@ -3152,7 +3171,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>106</v>
       </c>
@@ -3179,7 +3198,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>59</v>
       </c>
@@ -3206,7 +3225,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>87</v>
       </c>
@@ -3227,7 +3246,7 @@
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>86</v>
       </c>
@@ -3254,7 +3273,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>88</v>
       </c>
@@ -3275,7 +3294,7 @@
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>85</v>
       </c>
@@ -3296,7 +3315,7 @@
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>96</v>
       </c>
@@ -3317,7 +3336,7 @@
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>105</v>
       </c>
@@ -3338,7 +3357,7 @@
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
     </row>
-    <row r="100" spans="1:9" ht="28.5">
+    <row r="100" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>34</v>
       </c>
@@ -3361,7 +3380,7 @@
       <c r="H100" s="4"/>
       <c r="I100" s="6"/>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>60</v>
       </c>
@@ -3388,7 +3407,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>61</v>
       </c>
@@ -3409,7 +3428,7 @@
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>100</v>
       </c>
@@ -3430,7 +3449,7 @@
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>83</v>
       </c>
@@ -3451,7 +3470,7 @@
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>98</v>
       </c>
@@ -3472,7 +3491,7 @@
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>90</v>
       </c>
@@ -3493,7 +3512,7 @@
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
     </row>
-    <row r="107" spans="1:9" ht="42.75">
+    <row r="107" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>35</v>
       </c>
@@ -3522,7 +3541,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>64</v>
       </c>
@@ -3543,7 +3562,7 @@
       <c r="H108" s="3"/>
       <c r="I108" s="3"/>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>110</v>
       </c>
@@ -3570,7 +3589,7 @@
         <v>45231</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>84</v>
       </c>
@@ -3591,7 +3610,7 @@
       <c r="H110" s="3"/>
       <c r="I110" s="3"/>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>93</v>
       </c>
@@ -3618,7 +3637,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>45</v>
       </c>
@@ -3639,7 +3658,7 @@
       <c r="H112" s="14"/>
       <c r="I112" s="14"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="15"/>
       <c r="B113" s="16"/>
       <c r="C113" s="16"/>
@@ -3650,7 +3669,7 @@
       <c r="H113" s="16"/>
       <c r="I113" s="16"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="15"/>
       <c r="B114" s="16"/>
       <c r="C114" s="16"/>
@@ -3661,7 +3680,7 @@
       <c r="H114" s="16"/>
       <c r="I114" s="16"/>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="15"/>
       <c r="B115" s="16"/>
       <c r="C115" s="16"/>
@@ -3672,7 +3691,7 @@
       <c r="H115" s="16"/>
       <c r="I115" s="16"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="15"/>
       <c r="B116" s="16"/>
       <c r="C116" s="16"/>
@@ -3683,7 +3702,7 @@
       <c r="H116" s="16"/>
       <c r="I116" s="16"/>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="15"/>
       <c r="B117" s="16"/>
       <c r="C117" s="16"/>
@@ -3694,7 +3713,7 @@
       <c r="H117" s="16"/>
       <c r="I117" s="16"/>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="15"/>
       <c r="B118" s="16"/>
       <c r="C118" s="16"/>
@@ -3705,7 +3724,7 @@
       <c r="H118" s="16"/>
       <c r="I118" s="16"/>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="15"/>
       <c r="B119" s="16"/>
       <c r="C119" s="16"/>
@@ -3716,7 +3735,7 @@
       <c r="H119" s="16"/>
       <c r="I119" s="16"/>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="15"/>
       <c r="B120" s="16"/>
       <c r="C120" s="16"/>
@@ -3727,7 +3746,7 @@
       <c r="H120" s="16"/>
       <c r="I120" s="16"/>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="15"/>
       <c r="B121" s="16"/>
       <c r="C121" s="16"/>
@@ -3738,7 +3757,7 @@
       <c r="H121" s="16"/>
       <c r="I121" s="16"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="15"/>
       <c r="B122" s="16"/>
       <c r="C122" s="16"/>
@@ -3776,9 +3795,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
@@ -3786,9 +3805,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>

--- a/Другое/Кино.xlsx
+++ b/Другое/Кино.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="288">
   <si>
     <t>№</t>
   </si>
@@ -884,28 +884,56 @@
   </si>
   <si>
     <t>Плечи</t>
+  </si>
+  <si>
+    <t>Становая</t>
+  </si>
+  <si>
+    <t>Чт</t>
+  </si>
+  <si>
+    <t>Выпады 2 по 10 с гантелями 10 кг</t>
+  </si>
+  <si>
+    <t>Рабочий вес 70 кг</t>
+  </si>
+  <si>
+    <t>Пн</t>
+  </si>
+  <si>
+    <t>Отжимания на отжималка 2по 10</t>
+  </si>
+  <si>
+    <t>Рабочий вес 20 кг - 4 подхода по 10 раз</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="181" formatCode="mmm\.yy"/>
-    <numFmt numFmtId="182" formatCode="0.0"/>
+    <numFmt numFmtId="180" formatCode="dd\.mmm"/>
+    <numFmt numFmtId="181" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="182" formatCode="mmm\.yy"/>
+    <numFmt numFmtId="183" formatCode="0.0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Cascadia Mono SemiBold"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1086,7 +1114,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.35"/>
+        <fgColor theme="3" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1289,12 +1317,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.25"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.25"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.25"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.25"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1426,221 +1469,232 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2010,4774 +2064,4774 @@
   <dimension ref="A1:I222"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.14159292035398" style="6"/>
-    <col min="2" max="2" width="24.858407079646" style="6" customWidth="1"/>
-    <col min="3" max="3" width="22.141592920354" style="6" customWidth="1"/>
-    <col min="4" max="4" width="43.283185840708" style="6" customWidth="1"/>
-    <col min="5" max="5" width="11.4247787610619" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.4247787610619" style="6" customWidth="1"/>
-    <col min="7" max="8" width="14.858407079646" style="6" customWidth="1"/>
-    <col min="9" max="9" width="16.283185840708" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="9.14159292035398" style="6"/>
+    <col min="1" max="1" width="9.14159292035398" style="9"/>
+    <col min="2" max="2" width="24.858407079646" style="9" customWidth="1"/>
+    <col min="3" max="3" width="22.141592920354" style="9" customWidth="1"/>
+    <col min="4" max="4" width="43.283185840708" style="9" customWidth="1"/>
+    <col min="5" max="5" width="11.4247787610619" style="9" customWidth="1"/>
+    <col min="6" max="6" width="16.4247787610619" style="9" customWidth="1"/>
+    <col min="7" max="8" width="14.858407079646" style="9" customWidth="1"/>
+    <col min="9" max="9" width="16.283185840708" style="9" customWidth="1"/>
+    <col min="10" max="16384" width="9.14159292035398" style="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8">
+      <c r="A2" s="11">
         <v>6</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>1938</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="13">
         <v>7.7</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="11"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="8">
+      <c r="A3" s="11">
         <v>7</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>1940</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="13">
         <v>7.8</v>
       </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="11"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="8">
+      <c r="A4" s="11">
         <v>8</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>1946</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="13">
         <v>7.4</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="8">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>1954</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="13">
         <v>8</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="8">
+      <c r="G5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="11">
         <v>7</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="15">
         <v>46187</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="8">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>1954</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="13">
         <v>8.1</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="11"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="8">
+      <c r="A7" s="11">
         <v>11</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>1954</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="11">
         <v>8</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="11"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="8">
+      <c r="A8" s="11">
         <v>9</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>1957</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="13">
         <v>8</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="11"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="8">
+      <c r="A9" s="11">
         <v>12</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>1957</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="11">
         <v>8</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="11"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="14"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="8">
-        <v>15</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="11">
+        <v>15</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="11">
         <v>1957</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="11">
         <v>8.1</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="11"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="14"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="8">
+      <c r="A11" s="11">
         <v>4</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="11">
         <v>1958</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="13">
         <v>7.9</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="11"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="8">
+      <c r="A12" s="11">
         <v>1</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="11">
         <v>1960</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="13">
         <v>8.1</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="G12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="11">
         <v>8</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="15">
         <v>46184</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="8">
+      <c r="A13" s="11">
         <v>13</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="11">
         <v>1960</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="11">
         <v>7.9</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="8">
+      <c r="A14" s="11">
         <v>2</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="11">
         <v>1963</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="13">
         <v>7.5</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="11"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="14"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="8">
+      <c r="A15" s="11">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="11">
         <v>1963</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="11">
         <v>8</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="11"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="14"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="8">
+      <c r="A16" s="11">
         <v>16</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="11">
         <v>1964</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="11">
         <v>8</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="11"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="14"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="8">
+      <c r="A17" s="11">
         <v>10</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="11">
         <v>1966</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="13">
         <v>7.9</v>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="11"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="14"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="8">
+      <c r="A18" s="11">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="11">
         <v>1968</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="11">
         <v>7.9</v>
       </c>
-      <c r="G18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="8">
+      <c r="G18" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="11">
         <v>9</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="16">
         <v>45931</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="8">
+      <c r="A19" s="11">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="11">
         <v>1971</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="11">
         <v>7.9</v>
       </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="11"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="14"/>
     </row>
     <row r="20" ht="27" spans="1:9">
-      <c r="A20" s="8">
+      <c r="A20" s="11">
         <v>36</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="11">
         <v>1972</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="11">
         <v>8.7</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="16">
+      <c r="G20" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="19">
         <v>8</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="16">
         <v>46082</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="8">
+      <c r="A21" s="11">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="11">
         <v>1973</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="11">
         <v>7.1</v>
       </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="11"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="14"/>
     </row>
     <row r="22" ht="27" spans="1:9">
-      <c r="A22" s="8">
+      <c r="A22" s="11">
         <v>37</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="11">
         <v>1974</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="11">
         <v>8.5</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="8">
+      <c r="A23" s="11">
         <v>39</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="14" t="s">
+      <c r="C23" s="20"/>
+      <c r="D23" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="11">
         <v>1974</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="11">
         <v>7.6</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="8">
+      <c r="A24" s="11">
         <v>21</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="11">
         <v>1976</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="11">
         <v>7.7</v>
       </c>
-      <c r="G24" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="8">
+      <c r="G24" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="11">
         <v>7</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="16">
         <v>45839</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="8">
+      <c r="A25" s="11">
         <v>41</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17" t="s">
+      <c r="C25" s="20"/>
+      <c r="D25" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="11">
         <v>1976</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="11">
         <v>7.2</v>
       </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="8">
+      <c r="A26" s="11">
         <v>49</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17" t="s">
+      <c r="C26" s="20"/>
+      <c r="D26" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="11">
         <v>1977</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="11">
         <v>7.3</v>
       </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="8">
+      <c r="A27" s="11">
         <v>40</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="14" t="s">
+      <c r="C27" s="20"/>
+      <c r="D27" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="11">
         <v>1979</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="11">
         <v>8.2</v>
       </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="8">
+      <c r="A28" s="11">
         <v>19</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="11">
         <v>1980</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="11">
         <v>7.8</v>
       </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="11"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="14"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="8">
+      <c r="A29" s="11">
         <v>22</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="11">
         <v>1980</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="11">
         <v>7.8</v>
       </c>
-      <c r="G29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="8">
+      <c r="G29" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="11">
         <v>6</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="16">
         <v>45870</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="8">
+      <c r="A30" s="11">
         <v>42</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17" t="s">
+      <c r="C30" s="20"/>
+      <c r="D30" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="11">
         <v>1980</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="11">
         <v>6.7</v>
       </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="8">
+      <c r="A31" s="11">
         <v>23</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="11">
         <v>1982</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="11">
         <v>7.6</v>
       </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="11"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="14"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="8">
+      <c r="A32" s="11">
         <v>43</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17" t="s">
+      <c r="C32" s="20"/>
+      <c r="D32" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="11">
         <v>1983</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="11">
         <v>8.2</v>
       </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="8">
+      <c r="A33" s="11">
         <v>75</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17" t="s">
+      <c r="C33" s="20"/>
+      <c r="D33" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="11">
         <v>1984</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="11">
         <v>7.3</v>
       </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="8">
+      <c r="A34" s="11">
         <v>27</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="11">
         <v>1985</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="11">
         <v>7.5</v>
       </c>
-      <c r="G34" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="8">
+      <c r="G34" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="11">
         <v>6</v>
       </c>
-      <c r="I34" s="13">
+      <c r="I34" s="16">
         <v>45839</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="8">
+      <c r="A35" s="11">
         <v>48</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17" t="s">
+      <c r="C35" s="20"/>
+      <c r="D35" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="11">
         <v>1986</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="11">
         <v>7.5</v>
       </c>
-      <c r="G35" s="9"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="8">
+      <c r="A36" s="11">
         <v>44</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17" t="s">
+      <c r="C36" s="20"/>
+      <c r="D36" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="11">
         <v>1987</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="11">
         <v>7.8</v>
       </c>
-      <c r="G36" s="9"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="8">
+      <c r="A37" s="11">
         <v>24</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="11">
         <v>1988</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="11">
         <v>7.4</v>
       </c>
-      <c r="G37" s="9"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="11"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="14"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="8">
+      <c r="A38" s="11">
         <v>25</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="11">
         <v>1990</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="11">
         <v>8.1</v>
       </c>
-      <c r="G38" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" s="8">
+      <c r="G38" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="11">
         <v>9</v>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="16">
         <v>45809</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="8">
+      <c r="A39" s="11">
         <v>38</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="11">
         <v>1990</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="11">
         <v>7.9</v>
       </c>
-      <c r="G39" s="9"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="8">
+      <c r="A40" s="11">
         <v>76</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17" t="s">
+      <c r="C40" s="20"/>
+      <c r="D40" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="11">
         <v>1990</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="11">
         <v>7.6</v>
       </c>
-      <c r="G40" s="9"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="8">
+      <c r="A41" s="11">
         <v>28</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="11">
         <v>1991</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="11">
         <v>7.2</v>
       </c>
-      <c r="G41" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" s="8">
+      <c r="G41" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="11">
         <v>7</v>
       </c>
-      <c r="I41" s="13">
+      <c r="I41" s="16">
         <v>45839</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="8">
+      <c r="A42" s="11">
         <v>80</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17" t="s">
+      <c r="C42" s="20"/>
+      <c r="D42" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="11">
         <v>1991</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="11">
         <v>7.7</v>
       </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="8">
+      <c r="A43" s="11">
         <v>51</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17" t="s">
+      <c r="C43" s="20"/>
+      <c r="D43" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="11">
         <v>1992</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="11">
         <v>8.1</v>
       </c>
-      <c r="G43" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" s="16">
+      <c r="G43" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="19">
         <v>8</v>
       </c>
-      <c r="I43" s="13">
+      <c r="I43" s="16">
         <v>45748</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="8">
+      <c r="A44" s="11">
         <v>127</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="11">
         <v>1992</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="11">
         <v>8.5</v>
       </c>
-      <c r="G44" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H44" s="8">
+      <c r="G44" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="11">
         <v>6.5</v>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="21">
         <v>45778</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="8">
+      <c r="A45" s="11">
         <v>52</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17" t="s">
+      <c r="C45" s="20"/>
+      <c r="D45" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="11">
         <v>1994</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="11">
         <v>8.7</v>
       </c>
-      <c r="G45" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H45" s="16">
+      <c r="G45" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="19">
         <v>7</v>
       </c>
-      <c r="I45" s="13">
+      <c r="I45" s="16">
         <v>45748</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="8">
+      <c r="A46" s="11">
         <v>26</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="11">
         <v>1995</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="11">
         <v>8.1</v>
       </c>
-      <c r="G46" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H46" s="8">
+      <c r="G46" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="11">
         <v>8</v>
       </c>
-      <c r="I46" s="13">
+      <c r="I46" s="16">
         <v>45809</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="8">
+      <c r="A47" s="11">
         <v>70</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17" t="s">
+      <c r="C47" s="20"/>
+      <c r="D47" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="11">
         <v>1995</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="11">
         <v>8.3</v>
       </c>
-      <c r="G47" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" s="16">
+      <c r="G47" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="19">
         <v>8</v>
       </c>
-      <c r="I47" s="13">
+      <c r="I47" s="16">
         <v>46023</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="8">
+      <c r="A48" s="11">
         <v>72</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17" t="s">
+      <c r="C48" s="20"/>
+      <c r="D48" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="11">
         <v>1996</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="11">
         <v>7.6</v>
       </c>
-      <c r="G48" s="9"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="8">
+      <c r="A49" s="11">
         <v>46</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17" t="s">
+      <c r="C49" s="20"/>
+      <c r="D49" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="11">
         <v>1997</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="11">
         <v>7.3</v>
       </c>
-      <c r="G49" s="9"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="8">
+      <c r="A50" s="11">
         <v>53</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17" t="s">
+      <c r="C50" s="20"/>
+      <c r="D50" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="11">
         <v>1997</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="11">
         <v>7.1</v>
       </c>
-      <c r="G50" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H50" s="16">
+      <c r="G50" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="19">
         <v>5</v>
       </c>
-      <c r="I50" s="13">
+      <c r="I50" s="16">
         <v>45748</v>
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="8">
+      <c r="A51" s="11">
         <v>65</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17" t="s">
+      <c r="C51" s="20"/>
+      <c r="D51" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="11">
         <v>1997</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="11">
         <v>8.3</v>
       </c>
-      <c r="G51" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H51" s="16">
+      <c r="G51" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="19">
         <v>8</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="8">
+      <c r="A52" s="11">
         <v>95</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17" t="s">
+      <c r="C52" s="20"/>
+      <c r="D52" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="11">
         <v>1997</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="11">
         <v>7.4</v>
       </c>
-      <c r="G52" s="9"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="8">
+      <c r="A53" s="11">
         <v>74</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17" t="s">
+      <c r="C53" s="20"/>
+      <c r="D53" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="11">
         <v>1998</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="11">
         <v>7.8</v>
       </c>
-      <c r="G53" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H53" s="16">
+      <c r="G53" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="19">
         <v>6</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="8">
+      <c r="A54" s="11">
         <v>101</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17" t="s">
+      <c r="C54" s="20"/>
+      <c r="D54" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="11">
         <v>1998</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="11">
         <v>7.5</v>
       </c>
-      <c r="G54" s="9"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="17"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="8">
+      <c r="A55" s="11">
         <v>112</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17" t="s">
+      <c r="C55" s="20"/>
+      <c r="D55" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="11">
         <v>1998</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="11">
         <v>8.6</v>
       </c>
-      <c r="G55" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H55" s="8">
+      <c r="G55" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="11">
         <v>6</v>
       </c>
-      <c r="I55" s="18">
+      <c r="I55" s="21">
         <v>45717</v>
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="8">
+      <c r="A56" s="11">
         <v>50</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17" t="s">
+      <c r="C56" s="20"/>
+      <c r="D56" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="11">
         <v>1999</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="11">
         <v>7.8</v>
       </c>
-      <c r="G56" s="9"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="8">
+      <c r="A57" s="11">
         <v>66</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17" t="s">
+      <c r="C57" s="20"/>
+      <c r="D57" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="11">
         <v>1999</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="11">
         <v>8.7</v>
       </c>
-      <c r="G57" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H57" s="16">
+      <c r="G57" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="19">
         <v>8</v>
       </c>
-      <c r="I57" s="13">
+      <c r="I57" s="16">
         <v>46023</v>
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="8">
+      <c r="A58" s="11">
         <v>97</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17" t="s">
+      <c r="C58" s="20"/>
+      <c r="D58" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="11">
         <v>1999</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="11">
         <v>7.4</v>
       </c>
-      <c r="G58" s="9"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="8">
+      <c r="A59" s="11">
         <v>130</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17" t="s">
+      <c r="C59" s="20"/>
+      <c r="D59" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="11">
         <v>1999</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="11">
         <v>7.4</v>
       </c>
-      <c r="G59" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H59" s="8">
+      <c r="G59" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="11">
         <v>6</v>
       </c>
-      <c r="I59" s="18">
+      <c r="I59" s="21">
         <v>45778</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="8">
+      <c r="A60" s="11">
         <v>92</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="17"/>
-      <c r="D60" s="19" t="s">
+      <c r="C60" s="20"/>
+      <c r="D60" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="11">
         <v>2000</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="11">
         <v>8</v>
       </c>
-      <c r="G60" s="9"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="8">
+      <c r="A61" s="11">
         <v>108</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17" t="s">
+      <c r="C61" s="20"/>
+      <c r="D61" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="11">
         <v>2000</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="11">
         <v>7.9</v>
       </c>
-      <c r="G61" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="16">
+      <c r="G61" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="19">
         <v>8</v>
       </c>
-      <c r="I61" s="13">
+      <c r="I61" s="16">
         <v>46082</v>
       </c>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="8">
+      <c r="A62" s="11">
         <v>113</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17" t="s">
+      <c r="C62" s="20"/>
+      <c r="D62" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="11">
         <v>2000</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="11">
         <v>8.6</v>
       </c>
-      <c r="G62" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H62" s="8">
+      <c r="G62" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="11">
         <v>7</v>
       </c>
-      <c r="I62" s="18">
+      <c r="I62" s="21">
         <v>45717</v>
       </c>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="8">
+      <c r="A63" s="11">
         <v>47</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17" t="s">
+      <c r="C63" s="20"/>
+      <c r="D63" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="11">
         <v>2001</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="11">
         <v>7.7</v>
       </c>
-      <c r="G63" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H63" s="16">
+      <c r="G63" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="19">
         <v>7</v>
       </c>
-      <c r="I63" s="13">
+      <c r="I63" s="16">
         <v>45931</v>
       </c>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="8">
+      <c r="A64" s="11">
         <v>77</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17" t="s">
+      <c r="C64" s="20"/>
+      <c r="D64" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="11">
         <v>2001</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="11">
         <v>7.6</v>
       </c>
-      <c r="G64" s="9"/>
-      <c r="H64" s="17"/>
-      <c r="I64" s="17"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
     </row>
     <row r="65" ht="27" spans="1:9">
-      <c r="A65" s="8">
+      <c r="A65" s="11">
         <v>31</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="C65" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="D65" s="9" t="s">
+      <c r="D65" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="E65" s="8">
+      <c r="E65" s="11">
         <v>2002</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="11">
         <v>7.7</v>
       </c>
-      <c r="G65" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" s="8">
+      <c r="G65" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="11">
         <v>8</v>
       </c>
-      <c r="I65" s="13">
+      <c r="I65" s="16">
         <v>45839</v>
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="8">
+      <c r="A66" s="11">
         <v>63</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17" t="s">
+      <c r="C66" s="20"/>
+      <c r="D66" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="11">
         <v>2002</v>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="11">
         <v>7.3</v>
       </c>
-      <c r="G66" s="9"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="8">
+      <c r="A67" s="11">
         <v>102</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17" t="s">
+      <c r="C67" s="20"/>
+      <c r="D67" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="11">
         <v>2002</v>
       </c>
-      <c r="F67" s="8">
+      <c r="F67" s="11">
         <v>7.4</v>
       </c>
-      <c r="G67" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H67" s="16">
+      <c r="G67" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="19">
         <v>6</v>
       </c>
-      <c r="I67" s="13">
+      <c r="I67" s="16">
         <v>46143</v>
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="8">
+      <c r="A68" s="11">
         <v>54</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17" t="s">
+      <c r="C68" s="20"/>
+      <c r="D68" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="E68" s="8">
+      <c r="E68" s="11">
         <v>2003</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="11">
         <v>7.7</v>
       </c>
-      <c r="G68" s="9"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="8">
+      <c r="A69" s="11">
         <v>89</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17" t="s">
+      <c r="C69" s="20"/>
+      <c r="D69" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="E69" s="8">
+      <c r="E69" s="11">
         <v>2003</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="11">
         <v>8.1</v>
       </c>
-      <c r="G69" s="9"/>
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="8">
+      <c r="A70" s="11">
         <v>218</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17" t="s">
+      <c r="C70" s="20"/>
+      <c r="D70" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="11">
         <v>2003</v>
       </c>
-      <c r="F70" s="8"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="21"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="24"/>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="8">
+      <c r="A71" s="11">
         <v>29</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="D71" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="11">
         <v>2004</v>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="11">
         <v>7.6</v>
       </c>
-      <c r="G71" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" s="8">
+      <c r="G71" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="11">
         <v>8</v>
       </c>
-      <c r="I71" s="13">
+      <c r="I71" s="16">
         <v>45839</v>
       </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="8">
+      <c r="A72" s="11">
         <v>55</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17" t="s">
+      <c r="C72" s="20"/>
+      <c r="D72" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="E72" s="8">
+      <c r="E72" s="11">
         <v>2004</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="11">
         <v>7.6</v>
       </c>
-      <c r="G72" s="9"/>
-      <c r="H72" s="17"/>
-      <c r="I72" s="17"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="8">
+      <c r="A73" s="11">
         <v>91</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17" t="s">
+      <c r="C73" s="20"/>
+      <c r="D73" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="11">
         <v>2005</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="11">
         <v>7.6</v>
       </c>
-      <c r="G73" s="9"/>
-      <c r="H73" s="17"/>
-      <c r="I73" s="17"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="8">
+      <c r="A74" s="11">
         <v>103</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="17"/>
-      <c r="D74" s="17" t="s">
+      <c r="C74" s="20"/>
+      <c r="D74" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="11">
         <v>2005</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="11">
         <v>7.9</v>
       </c>
-      <c r="G74" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H74" s="16">
+      <c r="G74" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="19">
         <v>7</v>
       </c>
-      <c r="I74" s="11" t="s">
+      <c r="I74" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="8">
+      <c r="A75" s="11">
         <v>114</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="B75" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C75" s="17"/>
-      <c r="D75" s="17" t="s">
+      <c r="C75" s="20"/>
+      <c r="D75" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="11">
         <v>2005</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="11">
         <v>7.3</v>
       </c>
-      <c r="G75" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H75" s="8">
+      <c r="G75" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="11">
         <v>6</v>
       </c>
-      <c r="I75" s="18">
+      <c r="I75" s="21">
         <v>45748</v>
       </c>
     </row>
     <row r="76" ht="40.5" spans="1:9">
-      <c r="A76" s="8">
+      <c r="A76" s="11">
         <v>30</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C76" s="20" t="s">
+      <c r="C76" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D76" s="9" t="s">
+      <c r="D76" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="11">
         <v>2006</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="11">
         <v>8.5</v>
       </c>
-      <c r="G76" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" s="8">
+      <c r="G76" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="11">
         <v>8</v>
       </c>
-      <c r="I76" s="13">
+      <c r="I76" s="16">
         <v>45839</v>
       </c>
     </row>
     <row r="77" spans="1:9">
-      <c r="A77" s="8">
+      <c r="A77" s="11">
         <v>104</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17" t="s">
+      <c r="C77" s="20"/>
+      <c r="D77" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="11">
         <v>2006</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="11">
         <v>8.5</v>
       </c>
-      <c r="G77" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H77" s="16">
+      <c r="G77" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="19">
         <v>8</v>
       </c>
-      <c r="I77" s="11" t="s">
+      <c r="I77" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78" s="8">
+      <c r="A78" s="11">
         <v>56</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C78" s="17"/>
-      <c r="D78" s="17" t="s">
+      <c r="C78" s="20"/>
+      <c r="D78" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="11">
         <v>2007</v>
       </c>
-      <c r="F78" s="8">
+      <c r="F78" s="11">
         <v>7.1</v>
       </c>
-      <c r="G78" s="9"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="17"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="20"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="8">
+      <c r="A79" s="11">
         <v>71</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17" t="s">
+      <c r="C79" s="20"/>
+      <c r="D79" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="11">
         <v>2007</v>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="11">
         <v>7.3</v>
       </c>
-      <c r="G79" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" s="16">
+      <c r="G79" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="19">
         <v>8</v>
       </c>
-      <c r="I79" s="11" t="s">
+      <c r="I79" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:9">
-      <c r="A80" s="8">
+      <c r="A80" s="11">
         <v>73</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17" t="s">
+      <c r="C80" s="20"/>
+      <c r="D80" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="E80" s="8">
+      <c r="E80" s="11">
         <v>2007</v>
       </c>
-      <c r="F80" s="8">
+      <c r="F80" s="11">
         <v>7.8</v>
       </c>
-      <c r="G80" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="16">
+      <c r="G80" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="19">
         <v>7</v>
       </c>
-      <c r="I80" s="13">
+      <c r="I80" s="16">
         <v>45962</v>
       </c>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="8">
+      <c r="A81" s="11">
         <v>94</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B81" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17" t="s">
+      <c r="C81" s="20"/>
+      <c r="D81" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="E81" s="8">
+      <c r="E81" s="11">
         <v>2007</v>
       </c>
-      <c r="F81" s="8">
+      <c r="F81" s="11">
         <v>7.9</v>
       </c>
-      <c r="G81" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H81" s="16">
+      <c r="G81" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" s="19">
         <v>9</v>
       </c>
-      <c r="I81" s="13">
+      <c r="I81" s="16">
         <v>45839</v>
       </c>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="8">
+      <c r="A82" s="11">
         <v>62</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C82" s="17"/>
-      <c r="D82" s="15" t="s">
+      <c r="C82" s="20"/>
+      <c r="D82" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="E82" s="8">
+      <c r="E82" s="11">
         <v>2008</v>
       </c>
-      <c r="F82" s="8">
+      <c r="F82" s="11">
         <v>8.1</v>
       </c>
-      <c r="G82" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H82" s="16">
+      <c r="G82" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="19">
         <v>8</v>
       </c>
-      <c r="I82" s="11">
+      <c r="I82" s="14">
         <v>2024</v>
       </c>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" s="8">
+      <c r="A83" s="11">
         <v>78</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17" t="s">
+      <c r="C83" s="20"/>
+      <c r="D83" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E83" s="8">
+      <c r="E83" s="11">
         <v>2008</v>
       </c>
-      <c r="F83" s="8">
+      <c r="F83" s="11">
         <v>6.9</v>
       </c>
-      <c r="G83" s="9"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="17"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
     </row>
     <row r="84" spans="1:9">
-      <c r="A84" s="8">
+      <c r="A84" s="11">
         <v>111</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17" t="s">
+      <c r="C84" s="20"/>
+      <c r="D84" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="11">
         <v>2008</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="11">
         <v>8.5</v>
       </c>
-      <c r="G84" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" s="22">
+      <c r="G84" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="25">
         <v>7.7</v>
       </c>
-      <c r="I84" s="12">
+      <c r="I84" s="15">
         <v>46200</v>
       </c>
     </row>
     <row r="85" spans="1:9">
-      <c r="A85" s="8">
+      <c r="A85" s="11">
         <v>115</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="17"/>
-      <c r="D85" s="17" t="s">
+      <c r="C85" s="20"/>
+      <c r="D85" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="E85" s="8">
+      <c r="E85" s="11">
         <v>2008</v>
       </c>
-      <c r="F85" s="8">
+      <c r="F85" s="11">
         <v>7.8</v>
       </c>
-      <c r="G85" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H85" s="8">
+      <c r="G85" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="11">
         <v>6</v>
       </c>
-      <c r="I85" s="18">
+      <c r="I85" s="21">
         <v>45748</v>
       </c>
     </row>
     <row r="86" spans="1:9">
-      <c r="A86" s="8">
+      <c r="A86" s="11">
         <v>131</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="E86" s="8">
+      <c r="E86" s="11">
         <v>2008</v>
       </c>
-      <c r="F86" s="8">
+      <c r="F86" s="11">
         <v>6.8</v>
       </c>
-      <c r="G86" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H86" s="8">
+      <c r="G86" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="11">
         <v>6</v>
       </c>
-      <c r="I86" s="18">
+      <c r="I86" s="21">
         <v>45778</v>
       </c>
     </row>
     <row r="87" spans="1:9">
-      <c r="A87" s="8">
+      <c r="A87" s="11">
         <v>33</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="9" t="s">
+      <c r="C87" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D87" s="9" t="s">
+      <c r="D87" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E87" s="8">
+      <c r="E87" s="11">
         <v>2009</v>
       </c>
-      <c r="F87" s="8">
+      <c r="F87" s="11">
         <v>8.6</v>
       </c>
-      <c r="G87" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H87" s="8">
+      <c r="G87" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="11">
         <v>9</v>
       </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:9">
-      <c r="A88" s="8">
+      <c r="A88" s="11">
         <v>57</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C88" s="17"/>
-      <c r="D88" s="17" t="s">
+      <c r="C88" s="20"/>
+      <c r="D88" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="E88" s="8">
+      <c r="E88" s="11">
         <v>2009</v>
       </c>
-      <c r="F88" s="8">
+      <c r="F88" s="11">
         <v>8</v>
       </c>
-      <c r="G88" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" s="16">
+      <c r="G88" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="19">
         <v>7</v>
       </c>
-      <c r="I88" s="13">
+      <c r="I88" s="16">
         <v>45748</v>
       </c>
     </row>
     <row r="89" spans="1:9">
-      <c r="A89" s="8">
+      <c r="A89" s="11">
         <v>116</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C89" s="17"/>
-      <c r="D89" s="17" t="s">
+      <c r="C89" s="20"/>
+      <c r="D89" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E89" s="8">
+      <c r="E89" s="11">
         <v>2009</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="11">
         <v>8.1</v>
       </c>
-      <c r="G89" s="9"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="17"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="20"/>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" s="8">
+      <c r="A90" s="11">
         <v>58</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C90" s="17"/>
-      <c r="D90" s="17" t="s">
+      <c r="C90" s="20"/>
+      <c r="D90" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E90" s="8">
+      <c r="E90" s="11">
         <v>2010</v>
       </c>
-      <c r="F90" s="8">
+      <c r="F90" s="11">
         <v>8.3</v>
       </c>
-      <c r="G90" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" s="16">
+      <c r="G90" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="19">
         <v>7</v>
       </c>
-      <c r="I90" s="13">
+      <c r="I90" s="16">
         <v>45748</v>
       </c>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" s="8">
+      <c r="A91" s="11">
         <v>69</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17" t="s">
+      <c r="C91" s="20"/>
+      <c r="D91" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="E91" s="8">
+      <c r="E91" s="11">
         <v>2010</v>
       </c>
-      <c r="F91" s="8">
+      <c r="F91" s="11">
         <v>7.7</v>
       </c>
-      <c r="G91" s="9"/>
-      <c r="H91" s="17"/>
-      <c r="I91" s="17"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="20"/>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" s="8">
+      <c r="A92" s="11">
         <v>79</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C92" s="17"/>
-      <c r="D92" s="17" t="s">
+      <c r="C92" s="20"/>
+      <c r="D92" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="E92" s="8">
+      <c r="E92" s="11">
         <v>2010</v>
       </c>
-      <c r="F92" s="8">
+      <c r="F92" s="11">
         <v>7.6</v>
       </c>
-      <c r="G92" s="9"/>
-      <c r="H92" s="17"/>
-      <c r="I92" s="17"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="20"/>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="8">
+      <c r="A93" s="11">
         <v>82</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C93" s="17"/>
-      <c r="D93" s="17" t="s">
+      <c r="C93" s="20"/>
+      <c r="D93" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="E93" s="8">
+      <c r="E93" s="11">
         <v>2010</v>
       </c>
-      <c r="F93" s="8">
+      <c r="F93" s="11">
         <v>8.1</v>
       </c>
-      <c r="G93" s="9"/>
-      <c r="H93" s="17"/>
-      <c r="I93" s="17"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="20"/>
+      <c r="I93" s="20"/>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="8">
+      <c r="A94" s="11">
         <v>109</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C94" s="17"/>
-      <c r="D94" s="17" t="s">
+      <c r="C94" s="20"/>
+      <c r="D94" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="E94" s="8">
+      <c r="E94" s="11">
         <v>2010</v>
       </c>
-      <c r="F94" s="8">
+      <c r="F94" s="11">
         <v>8.7</v>
       </c>
-      <c r="G94" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" s="16">
+      <c r="G94" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="19">
         <v>8</v>
       </c>
-      <c r="I94" s="11" t="s">
+      <c r="I94" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" s="8">
+      <c r="A95" s="11">
         <v>219</v>
       </c>
-      <c r="B95" s="14" t="s">
+      <c r="B95" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C95" s="17" t="s">
+      <c r="C95" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="D95" s="17" t="s">
+      <c r="D95" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="E95" s="8">
+      <c r="E95" s="11">
         <v>2010</v>
       </c>
-      <c r="F95" s="8">
+      <c r="F95" s="11">
         <v>7.6</v>
       </c>
-      <c r="G95" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" s="8">
+      <c r="G95" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="11">
         <v>7.1</v>
       </c>
-      <c r="I95" s="21">
+      <c r="I95" s="24">
         <v>46200</v>
       </c>
     </row>
     <row r="96" spans="1:9">
-      <c r="A96" s="8">
+      <c r="A96" s="11">
         <v>67</v>
       </c>
-      <c r="B96" s="14" t="s">
+      <c r="B96" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C96" s="17"/>
-      <c r="D96" s="17" t="s">
+      <c r="C96" s="20"/>
+      <c r="D96" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E96" s="8">
+      <c r="E96" s="11">
         <v>2011</v>
       </c>
-      <c r="F96" s="8">
+      <c r="F96" s="11">
         <v>7.8</v>
       </c>
-      <c r="G96" s="9"/>
-      <c r="H96" s="17"/>
-      <c r="I96" s="17"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="20"/>
+      <c r="I96" s="20"/>
     </row>
     <row r="97" spans="1:9">
-      <c r="A97" s="8">
+      <c r="A97" s="11">
         <v>117</v>
       </c>
-      <c r="B97" s="14" t="s">
+      <c r="B97" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C97" s="17"/>
-      <c r="D97" s="17" t="s">
+      <c r="C97" s="20"/>
+      <c r="D97" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E97" s="8">
+      <c r="E97" s="11">
         <v>2011</v>
       </c>
-      <c r="F97" s="8">
+      <c r="F97" s="11">
         <v>7.9</v>
       </c>
-      <c r="G97" s="9"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="17"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="20"/>
     </row>
     <row r="98" spans="1:9">
-      <c r="A98" s="8">
+      <c r="A98" s="11">
         <v>99</v>
       </c>
-      <c r="B98" s="14" t="s">
+      <c r="B98" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C98" s="17"/>
-      <c r="D98" s="17" t="s">
+      <c r="C98" s="20"/>
+      <c r="D98" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="E98" s="8">
+      <c r="E98" s="11">
         <v>2012</v>
       </c>
-      <c r="F98" s="8">
+      <c r="F98" s="11">
         <v>6.8</v>
       </c>
-      <c r="G98" s="9"/>
-      <c r="H98" s="17"/>
-      <c r="I98" s="17"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="20"/>
+      <c r="I98" s="20"/>
     </row>
     <row r="99" spans="1:9">
-      <c r="A99" s="8">
+      <c r="A99" s="11">
         <v>107</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="B99" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C99" s="17"/>
-      <c r="D99" s="19" t="s">
+      <c r="C99" s="20"/>
+      <c r="D99" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="E99" s="8">
+      <c r="E99" s="11">
         <v>2012</v>
       </c>
-      <c r="F99" s="8">
+      <c r="F99" s="11">
         <v>8.2</v>
       </c>
-      <c r="G99" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" s="16">
+      <c r="G99" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="19">
         <v>8</v>
       </c>
-      <c r="I99" s="11" t="s">
+      <c r="I99" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="100" spans="1:9">
-      <c r="A100" s="8">
+      <c r="A100" s="11">
         <v>126</v>
       </c>
-      <c r="B100" s="14" t="s">
+      <c r="B100" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C100" s="17" t="s">
+      <c r="C100" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="E100" s="8">
+      <c r="E100" s="11">
         <v>2012</v>
       </c>
-      <c r="F100" s="8">
+      <c r="F100" s="11">
         <v>7.5</v>
       </c>
-      <c r="G100" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H100" s="8">
+      <c r="G100" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="11">
         <v>7</v>
       </c>
-      <c r="I100" s="18">
+      <c r="I100" s="21">
         <v>45748</v>
       </c>
     </row>
     <row r="101" ht="27" spans="1:9">
-      <c r="A101" s="8">
+      <c r="A101" s="11">
         <v>32</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C101" s="20" t="s">
+      <c r="C101" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="D101" s="9" t="s">
+      <c r="D101" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="E101" s="8">
+      <c r="E101" s="11">
         <v>2013</v>
       </c>
-      <c r="F101" s="8">
+      <c r="F101" s="11">
         <v>8.1</v>
       </c>
-      <c r="G101" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H101" s="8">
+      <c r="G101" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="11">
         <v>9</v>
       </c>
-      <c r="I101" s="11" t="s">
+      <c r="I101" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="8">
+      <c r="A102" s="11">
         <v>81</v>
       </c>
-      <c r="B102" s="14" t="s">
+      <c r="B102" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C102" s="17"/>
-      <c r="D102" s="17" t="s">
+      <c r="C102" s="20"/>
+      <c r="D102" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="E102" s="8">
+      <c r="E102" s="11">
         <v>2013</v>
       </c>
-      <c r="F102" s="8">
+      <c r="F102" s="11">
         <v>7.8</v>
       </c>
-      <c r="G102" s="9"/>
-      <c r="H102" s="17"/>
-      <c r="I102" s="17"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="20"/>
+      <c r="I102" s="20"/>
     </row>
     <row r="103" spans="1:9">
-      <c r="A103" s="8">
+      <c r="A103" s="11">
         <v>125</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C103" s="17" t="s">
+      <c r="C103" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D103" s="17" t="s">
+      <c r="D103" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="E103" s="8">
+      <c r="E103" s="11">
         <v>2013</v>
       </c>
-      <c r="F103" s="8">
+      <c r="F103" s="11">
         <v>8</v>
       </c>
-      <c r="G103" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H103" s="8">
+      <c r="G103" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="11">
         <v>9</v>
       </c>
-      <c r="I103" s="18">
+      <c r="I103" s="21">
         <v>45658</v>
       </c>
     </row>
     <row r="104" spans="1:9">
-      <c r="A104" s="8">
+      <c r="A104" s="11">
         <v>68</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C104" s="17"/>
-      <c r="D104" s="17" t="s">
+      <c r="C104" s="20"/>
+      <c r="D104" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="E104" s="8">
+      <c r="E104" s="11">
         <v>2014</v>
       </c>
-      <c r="F104" s="8">
+      <c r="F104" s="11">
         <v>8</v>
       </c>
-      <c r="G104" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H104" s="16">
+      <c r="G104" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="19">
         <v>8</v>
       </c>
-      <c r="I104" s="11" t="s">
+      <c r="I104" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="105" spans="1:9">
-      <c r="A105" s="8">
+      <c r="A105" s="11">
         <v>106</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B105" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C105" s="17" t="s">
+      <c r="C105" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D105" s="17" t="s">
+      <c r="D105" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="E105" s="8">
+      <c r="E105" s="11">
         <v>2014</v>
       </c>
-      <c r="F105" s="8">
+      <c r="F105" s="11">
         <v>8.7</v>
       </c>
-      <c r="G105" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H105" s="16">
+      <c r="G105" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="19">
         <v>10</v>
       </c>
-      <c r="I105" s="13">
+      <c r="I105" s="16">
         <v>46082</v>
       </c>
     </row>
     <row r="106" ht="27" spans="1:9">
-      <c r="A106" s="8">
+      <c r="A106" s="11">
         <v>128</v>
       </c>
-      <c r="B106" s="19" t="s">
+      <c r="B106" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="C106" s="17"/>
-      <c r="D106" s="14" t="s">
+      <c r="C106" s="20"/>
+      <c r="D106" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="E106" s="8">
+      <c r="E106" s="11">
         <v>2014</v>
       </c>
-      <c r="F106" s="8">
+      <c r="F106" s="11">
         <v>7.7</v>
       </c>
-      <c r="G106" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H106" s="8">
+      <c r="G106" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" s="11">
         <v>7</v>
       </c>
-      <c r="I106" s="18">
+      <c r="I106" s="21">
         <v>45778</v>
       </c>
     </row>
     <row r="107" spans="1:9">
-      <c r="A107" s="8">
+      <c r="A107" s="11">
         <v>59</v>
       </c>
-      <c r="B107" s="14" t="s">
+      <c r="B107" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C107" s="17"/>
-      <c r="D107" s="17" t="s">
+      <c r="C107" s="20"/>
+      <c r="D107" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="E107" s="8">
+      <c r="E107" s="11">
         <v>2015</v>
       </c>
-      <c r="F107" s="8">
+      <c r="F107" s="11">
         <v>8</v>
       </c>
-      <c r="G107" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H107" s="16">
+      <c r="G107" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="19">
         <v>8</v>
       </c>
-      <c r="I107" s="13">
+      <c r="I107" s="16">
         <v>45748</v>
       </c>
     </row>
     <row r="108" spans="1:9">
-      <c r="A108" s="8">
+      <c r="A108" s="11">
         <v>87</v>
       </c>
-      <c r="B108" s="14" t="s">
+      <c r="B108" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C108" s="17"/>
-      <c r="D108" s="17" t="s">
+      <c r="C108" s="20"/>
+      <c r="D108" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="E108" s="8">
+      <c r="E108" s="11">
         <v>2015</v>
       </c>
-      <c r="F108" s="8">
+      <c r="F108" s="11">
         <v>7.2</v>
       </c>
-      <c r="G108" s="9"/>
-      <c r="H108" s="17"/>
-      <c r="I108" s="17"/>
+      <c r="G108" s="12"/>
+      <c r="H108" s="20"/>
+      <c r="I108" s="20"/>
     </row>
     <row r="109" spans="1:9">
-      <c r="A109" s="8">
+      <c r="A109" s="11">
         <v>118</v>
       </c>
-      <c r="B109" s="14" t="s">
+      <c r="B109" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C109" s="17"/>
-      <c r="D109" s="17" t="s">
+      <c r="C109" s="20"/>
+      <c r="D109" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="E109" s="8">
+      <c r="E109" s="11">
         <v>2015</v>
       </c>
-      <c r="F109" s="8">
+      <c r="F109" s="11">
         <v>7.6</v>
       </c>
-      <c r="G109" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H109" s="8">
+      <c r="G109" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" s="11">
         <v>7</v>
       </c>
-      <c r="I109" s="17">
+      <c r="I109" s="20">
         <v>2023</v>
       </c>
     </row>
     <row r="110" spans="1:9">
-      <c r="A110" s="8">
+      <c r="A110" s="11">
         <v>86</v>
       </c>
-      <c r="B110" s="14" t="s">
+      <c r="B110" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C110" s="17"/>
-      <c r="D110" s="15" t="s">
+      <c r="C110" s="20"/>
+      <c r="D110" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="E110" s="8">
+      <c r="E110" s="11">
         <v>2016</v>
       </c>
-      <c r="F110" s="8">
+      <c r="F110" s="11">
         <v>7.6</v>
       </c>
-      <c r="G110" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H110" s="16">
+      <c r="G110" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" s="19">
         <v>7</v>
       </c>
-      <c r="I110" s="11" t="s">
+      <c r="I110" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="111" spans="1:9">
-      <c r="A111" s="8">
+      <c r="A111" s="11">
         <v>88</v>
       </c>
-      <c r="B111" s="14" t="s">
+      <c r="B111" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C111" s="17"/>
-      <c r="D111" s="17" t="s">
+      <c r="C111" s="20"/>
+      <c r="D111" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="E111" s="8">
+      <c r="E111" s="11">
         <v>2016</v>
       </c>
-      <c r="F111" s="8">
+      <c r="F111" s="11">
         <v>7.7</v>
       </c>
-      <c r="G111" s="9"/>
-      <c r="H111" s="17"/>
-      <c r="I111" s="17"/>
+      <c r="G111" s="12"/>
+      <c r="H111" s="20"/>
+      <c r="I111" s="20"/>
     </row>
     <row r="112" spans="1:9">
-      <c r="A112" s="8">
+      <c r="A112" s="11">
         <v>85</v>
       </c>
-      <c r="B112" s="23" t="s">
+      <c r="B112" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="C112" s="24"/>
-      <c r="D112" s="24" t="s">
+      <c r="C112" s="27"/>
+      <c r="D112" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="E112" s="25">
+      <c r="E112" s="28">
         <v>2017</v>
       </c>
-      <c r="F112" s="25">
+      <c r="F112" s="28">
         <v>7.8</v>
       </c>
-      <c r="G112" s="26"/>
-      <c r="H112" s="24"/>
-      <c r="I112" s="24"/>
+      <c r="G112" s="29"/>
+      <c r="H112" s="27"/>
+      <c r="I112" s="27"/>
     </row>
     <row r="113" spans="1:9">
-      <c r="A113" s="8">
+      <c r="A113" s="11">
         <v>96</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C113" s="17"/>
-      <c r="D113" s="17" t="s">
+      <c r="C113" s="20"/>
+      <c r="D113" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="E113" s="8">
+      <c r="E113" s="11">
         <v>2017</v>
       </c>
-      <c r="F113" s="8">
+      <c r="F113" s="11">
         <v>7.1</v>
       </c>
-      <c r="G113" s="9"/>
-      <c r="H113" s="17"/>
-      <c r="I113" s="17"/>
+      <c r="G113" s="12"/>
+      <c r="H113" s="20"/>
+      <c r="I113" s="20"/>
     </row>
     <row r="114" spans="1:9">
-      <c r="A114" s="8">
+      <c r="A114" s="11">
         <v>105</v>
       </c>
-      <c r="B114" s="14" t="s">
+      <c r="B114" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C114" s="17"/>
-      <c r="D114" s="17" t="s">
+      <c r="C114" s="20"/>
+      <c r="D114" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="E114" s="8">
+      <c r="E114" s="11">
         <v>2017</v>
       </c>
-      <c r="F114" s="8">
+      <c r="F114" s="11">
         <v>7.3</v>
       </c>
-      <c r="G114" s="9"/>
-      <c r="H114" s="17"/>
-      <c r="I114" s="17"/>
+      <c r="G114" s="12"/>
+      <c r="H114" s="20"/>
+      <c r="I114" s="20"/>
     </row>
     <row r="115" ht="27" spans="1:9">
-      <c r="A115" s="8">
+      <c r="A115" s="11">
         <v>34</v>
       </c>
-      <c r="B115" s="9" t="s">
+      <c r="B115" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C115" s="20" t="s">
+      <c r="C115" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="D115" s="9" t="s">
+      <c r="D115" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E115" s="8">
+      <c r="E115" s="11">
         <v>2019</v>
       </c>
-      <c r="F115" s="8">
+      <c r="F115" s="11">
         <v>7.4</v>
       </c>
-      <c r="G115" s="9"/>
-      <c r="H115" s="8"/>
-      <c r="I115" s="11"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="11"/>
+      <c r="I115" s="14"/>
     </row>
     <row r="116" spans="1:9">
-      <c r="A116" s="8">
+      <c r="A116" s="11">
         <v>60</v>
       </c>
-      <c r="B116" s="14" t="s">
+      <c r="B116" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C116" s="17"/>
-      <c r="D116" s="17" t="s">
+      <c r="C116" s="20"/>
+      <c r="D116" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="E116" s="8">
+      <c r="E116" s="11">
         <v>2019</v>
       </c>
-      <c r="F116" s="8">
+      <c r="F116" s="11">
         <v>7.7</v>
       </c>
-      <c r="G116" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H116" s="16">
+      <c r="G116" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="19">
         <v>7</v>
       </c>
-      <c r="I116" s="13">
+      <c r="I116" s="16">
         <v>45748</v>
       </c>
     </row>
     <row r="117" spans="1:9">
-      <c r="A117" s="8">
+      <c r="A117" s="11">
         <v>119</v>
       </c>
-      <c r="B117" s="14" t="s">
+      <c r="B117" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C117" s="17" t="s">
+      <c r="C117" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D117" s="17" t="s">
+      <c r="D117" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="E117" s="8">
+      <c r="E117" s="11">
         <v>2019</v>
       </c>
-      <c r="F117" s="8">
+      <c r="F117" s="11">
         <v>8.7</v>
       </c>
-      <c r="G117" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H117" s="8">
+      <c r="G117" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" s="11">
         <v>8</v>
       </c>
-      <c r="I117" s="27" t="s">
+      <c r="I117" s="30" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="118" spans="1:9">
-      <c r="A118" s="8">
+      <c r="A118" s="11">
         <v>129</v>
       </c>
-      <c r="B118" s="14" t="s">
+      <c r="B118" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C118" s="17"/>
-      <c r="D118" s="17" t="s">
+      <c r="C118" s="20"/>
+      <c r="D118" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="E118" s="8">
+      <c r="E118" s="11">
         <v>2019</v>
       </c>
-      <c r="F118" s="8">
+      <c r="F118" s="11">
         <v>8.1</v>
       </c>
-      <c r="G118" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H118" s="8">
+      <c r="G118" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" s="11">
         <v>7.5</v>
       </c>
-      <c r="I118" s="18">
+      <c r="I118" s="21">
         <v>45778</v>
       </c>
     </row>
     <row r="119" spans="1:9">
-      <c r="A119" s="8">
+      <c r="A119" s="11">
         <v>61</v>
       </c>
-      <c r="B119" s="14" t="s">
+      <c r="B119" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C119" s="17"/>
-      <c r="D119" s="17" t="s">
+      <c r="C119" s="20"/>
+      <c r="D119" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="E119" s="8">
+      <c r="E119" s="11">
         <v>2020</v>
       </c>
-      <c r="F119" s="8">
+      <c r="F119" s="11">
         <v>7</v>
       </c>
-      <c r="G119" s="9"/>
-      <c r="H119" s="17"/>
-      <c r="I119" s="17"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="20"/>
+      <c r="I119" s="20"/>
     </row>
     <row r="120" spans="1:9">
-      <c r="A120" s="8">
+      <c r="A120" s="11">
         <v>100</v>
       </c>
-      <c r="B120" s="14" t="s">
+      <c r="B120" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C120" s="17"/>
-      <c r="D120" s="17" t="s">
+      <c r="C120" s="20"/>
+      <c r="D120" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="E120" s="8">
+      <c r="E120" s="11">
         <v>2020</v>
       </c>
-      <c r="F120" s="8">
+      <c r="F120" s="11">
         <v>7.5</v>
       </c>
-      <c r="G120" s="9"/>
-      <c r="H120" s="17"/>
-      <c r="I120" s="17"/>
+      <c r="G120" s="12"/>
+      <c r="H120" s="20"/>
+      <c r="I120" s="20"/>
     </row>
     <row r="121" spans="1:9">
-      <c r="A121" s="8">
+      <c r="A121" s="11">
         <v>83</v>
       </c>
-      <c r="B121" s="14" t="s">
+      <c r="B121" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C121" s="17"/>
-      <c r="D121" s="17" t="s">
+      <c r="C121" s="20"/>
+      <c r="D121" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="E121" s="8">
+      <c r="E121" s="11">
         <v>2021</v>
       </c>
-      <c r="F121" s="8">
+      <c r="F121" s="11">
         <v>7.7</v>
       </c>
-      <c r="G121" s="9"/>
-      <c r="H121" s="17"/>
-      <c r="I121" s="17"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="20"/>
+      <c r="I121" s="20"/>
     </row>
     <row r="122" spans="1:9">
-      <c r="A122" s="8">
+      <c r="A122" s="11">
         <v>98</v>
       </c>
-      <c r="B122" s="14" t="s">
+      <c r="B122" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C122" s="17"/>
-      <c r="D122" s="17" t="s">
+      <c r="C122" s="20"/>
+      <c r="D122" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="E122" s="8">
+      <c r="E122" s="11">
         <v>2021</v>
       </c>
-      <c r="F122" s="8">
+      <c r="F122" s="11">
         <v>7</v>
       </c>
-      <c r="G122" s="9"/>
-      <c r="H122" s="17"/>
-      <c r="I122" s="17"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="20"/>
+      <c r="I122" s="20"/>
     </row>
     <row r="123" spans="1:9">
-      <c r="A123" s="8">
+      <c r="A123" s="11">
         <v>120</v>
       </c>
-      <c r="B123" s="14" t="s">
+      <c r="B123" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C123" s="17"/>
-      <c r="D123" s="17" t="s">
+      <c r="C123" s="20"/>
+      <c r="D123" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="E123" s="8">
+      <c r="E123" s="11">
         <v>2021</v>
       </c>
-      <c r="F123" s="8">
+      <c r="F123" s="11">
         <v>7.7</v>
       </c>
-      <c r="G123" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H123" s="8">
+      <c r="G123" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" s="11">
         <v>7</v>
       </c>
-      <c r="I123" s="27" t="s">
+      <c r="I123" s="30" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="124" spans="1:9">
-      <c r="A124" s="8">
+      <c r="A124" s="11">
         <v>90</v>
       </c>
-      <c r="B124" s="14" t="s">
+      <c r="B124" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C124" s="17"/>
-      <c r="D124" s="17" t="s">
+      <c r="C124" s="20"/>
+      <c r="D124" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="E124" s="8">
+      <c r="E124" s="11">
         <v>2022</v>
       </c>
-      <c r="F124" s="8">
+      <c r="F124" s="11">
         <v>7.1</v>
       </c>
-      <c r="G124" s="9"/>
-      <c r="H124" s="17"/>
-      <c r="I124" s="17"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="20"/>
+      <c r="I124" s="20"/>
     </row>
     <row r="125" spans="1:9">
-      <c r="A125" s="8">
+      <c r="A125" s="11">
         <v>121</v>
       </c>
-      <c r="B125" s="14" t="s">
+      <c r="B125" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C125" s="17"/>
-      <c r="D125" s="17" t="s">
+      <c r="C125" s="20"/>
+      <c r="D125" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="E125" s="8">
+      <c r="E125" s="11">
         <v>2022</v>
       </c>
-      <c r="F125" s="8">
+      <c r="F125" s="11">
         <v>7.9</v>
       </c>
-      <c r="G125" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H125" s="8">
+      <c r="G125" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" s="11">
         <v>7</v>
       </c>
-      <c r="I125" s="18">
+      <c r="I125" s="21">
         <v>44713</v>
       </c>
     </row>
     <row r="126" spans="1:9">
-      <c r="A126" s="8">
+      <c r="A126" s="11">
         <v>122</v>
       </c>
-      <c r="B126" s="14" t="s">
+      <c r="B126" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C126" s="17"/>
-      <c r="D126" s="15" t="s">
+      <c r="C126" s="20"/>
+      <c r="D126" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="E126" s="8">
+      <c r="E126" s="11">
         <v>2022</v>
       </c>
-      <c r="F126" s="8">
+      <c r="F126" s="11">
         <v>7.2</v>
       </c>
-      <c r="G126" s="9"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="17"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="11"/>
+      <c r="I126" s="20"/>
     </row>
     <row r="127" ht="27" spans="1:9">
-      <c r="A127" s="8">
+      <c r="A127" s="11">
         <v>35</v>
       </c>
-      <c r="B127" s="9" t="s">
+      <c r="B127" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C127" s="20" t="s">
+      <c r="C127" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="D127" s="9" t="s">
+      <c r="D127" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="E127" s="8">
+      <c r="E127" s="11">
         <v>2023</v>
       </c>
-      <c r="F127" s="8">
+      <c r="F127" s="11">
         <v>7.1</v>
       </c>
-      <c r="G127" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H127" s="16">
+      <c r="G127" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H127" s="19">
         <v>8</v>
       </c>
-      <c r="I127" s="13">
+      <c r="I127" s="16">
         <v>45717</v>
       </c>
     </row>
     <row r="128" spans="1:9">
-      <c r="A128" s="8">
+      <c r="A128" s="11">
         <v>64</v>
       </c>
-      <c r="B128" s="14" t="s">
+      <c r="B128" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C128" s="17"/>
-      <c r="D128" s="17" t="s">
+      <c r="C128" s="20"/>
+      <c r="D128" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="E128" s="8">
+      <c r="E128" s="11">
         <v>2023</v>
       </c>
-      <c r="F128" s="8">
+      <c r="F128" s="11">
         <v>6.6</v>
       </c>
-      <c r="G128" s="9"/>
-      <c r="H128" s="17"/>
-      <c r="I128" s="17"/>
+      <c r="G128" s="12"/>
+      <c r="H128" s="20"/>
+      <c r="I128" s="20"/>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="8">
+      <c r="A129" s="11">
         <v>110</v>
       </c>
-      <c r="B129" s="14" t="s">
+      <c r="B129" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C129" s="17"/>
-      <c r="D129" s="17" t="s">
+      <c r="C129" s="20"/>
+      <c r="D129" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="E129" s="8">
+      <c r="E129" s="11">
         <v>2023</v>
       </c>
-      <c r="F129" s="8">
+      <c r="F129" s="11">
         <v>8.1</v>
       </c>
-      <c r="G129" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H129" s="16">
+      <c r="G129" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" s="19">
         <v>7</v>
       </c>
-      <c r="I129" s="13">
+      <c r="I129" s="16">
         <v>45231</v>
       </c>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="8">
+      <c r="A130" s="11">
         <v>84</v>
       </c>
-      <c r="B130" s="14" t="s">
+      <c r="B130" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C130" s="17"/>
-      <c r="D130" s="17" t="s">
+      <c r="C130" s="20"/>
+      <c r="D130" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="E130" s="8">
+      <c r="E130" s="11">
         <v>2024</v>
       </c>
-      <c r="F130" s="8">
+      <c r="F130" s="11">
         <v>8.2</v>
       </c>
-      <c r="G130" s="9"/>
-      <c r="H130" s="17"/>
-      <c r="I130" s="17"/>
+      <c r="G130" s="12"/>
+      <c r="H130" s="20"/>
+      <c r="I130" s="20"/>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="8">
+      <c r="A131" s="11">
         <v>123</v>
       </c>
-      <c r="B131" s="14" t="s">
+      <c r="B131" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C131" s="17"/>
-      <c r="D131" s="17" t="s">
+      <c r="C131" s="20"/>
+      <c r="D131" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="E131" s="8">
+      <c r="E131" s="11">
         <v>2024</v>
       </c>
-      <c r="F131" s="8">
+      <c r="F131" s="11">
         <v>7.3</v>
       </c>
-      <c r="G131" s="9"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="17"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="11"/>
+      <c r="I131" s="20"/>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="8">
+      <c r="A132" s="11">
         <v>93</v>
       </c>
-      <c r="B132" s="14" t="s">
+      <c r="B132" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C132" s="17"/>
-      <c r="D132" s="17" t="s">
+      <c r="C132" s="20"/>
+      <c r="D132" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E132" s="8">
+      <c r="E132" s="11">
         <v>2025</v>
       </c>
-      <c r="F132" s="8">
+      <c r="F132" s="11">
         <v>7</v>
       </c>
-      <c r="G132" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H132" s="16">
+      <c r="G132" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" s="19">
         <v>7</v>
       </c>
-      <c r="I132" s="28" t="s">
+      <c r="I132" s="31" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="8">
+      <c r="A133" s="11">
         <v>124</v>
       </c>
-      <c r="B133" s="14" t="s">
+      <c r="B133" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C133" s="17"/>
-      <c r="D133" s="17" t="s">
+      <c r="C133" s="20"/>
+      <c r="D133" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="E133" s="8">
+      <c r="E133" s="11">
         <v>2026</v>
       </c>
-      <c r="F133" s="8">
+      <c r="F133" s="11">
         <v>6.6</v>
       </c>
-      <c r="G133" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H133" s="8">
+      <c r="G133" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H133" s="11">
         <v>6</v>
       </c>
-      <c r="I133" s="21">
+      <c r="I133" s="24">
         <v>46171</v>
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="8">
+      <c r="A134" s="11">
         <v>45</v>
       </c>
-      <c r="B134" s="14" t="s">
+      <c r="B134" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C134" s="17"/>
-      <c r="D134" s="17" t="s">
+      <c r="C134" s="20"/>
+      <c r="D134" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="E134" s="8" t="s">
+      <c r="E134" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="F134" s="8">
+      <c r="F134" s="11">
         <v>8.4</v>
       </c>
-      <c r="G134" s="9"/>
-      <c r="H134" s="17"/>
-      <c r="I134" s="17"/>
+      <c r="G134" s="12"/>
+      <c r="H134" s="20"/>
+      <c r="I134" s="20"/>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="8">
+      <c r="A135" s="11">
         <v>132</v>
       </c>
-      <c r="B135" s="14"/>
-      <c r="C135" s="17"/>
-      <c r="D135" s="17" t="s">
+      <c r="B135" s="17"/>
+      <c r="C135" s="20"/>
+      <c r="D135" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
-      <c r="G135" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H135" s="8"/>
-      <c r="I135" s="18">
+      <c r="E135" s="11"/>
+      <c r="F135" s="11"/>
+      <c r="G135" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" s="11"/>
+      <c r="I135" s="21">
         <v>45809</v>
       </c>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="8">
+      <c r="A136" s="11">
         <v>133</v>
       </c>
-      <c r="B136" s="14"/>
-      <c r="C136" s="17"/>
-      <c r="D136" s="17" t="s">
+      <c r="B136" s="17"/>
+      <c r="C136" s="20"/>
+      <c r="D136" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
-      <c r="G136" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H136" s="8"/>
-      <c r="I136" s="18">
+      <c r="E136" s="11"/>
+      <c r="F136" s="11"/>
+      <c r="G136" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" s="11"/>
+      <c r="I136" s="21">
         <v>45809</v>
       </c>
     </row>
     <row r="137" spans="1:9">
-      <c r="A137" s="8">
+      <c r="A137" s="11">
         <v>134</v>
       </c>
-      <c r="B137" s="14"/>
-      <c r="C137" s="17"/>
-      <c r="D137" s="17" t="s">
+      <c r="B137" s="17"/>
+      <c r="C137" s="20"/>
+      <c r="D137" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
-      <c r="G137" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H137" s="8"/>
-      <c r="I137" s="18">
+      <c r="E137" s="11"/>
+      <c r="F137" s="11"/>
+      <c r="G137" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" s="11"/>
+      <c r="I137" s="21">
         <v>45809</v>
       </c>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="8">
+      <c r="A138" s="11">
         <v>135</v>
       </c>
-      <c r="B138" s="14"/>
-      <c r="C138" s="17"/>
-      <c r="D138" s="17" t="s">
+      <c r="B138" s="17"/>
+      <c r="C138" s="20"/>
+      <c r="D138" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="E138" s="8"/>
-      <c r="F138" s="8"/>
-      <c r="G138" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H138" s="8"/>
-      <c r="I138" s="18">
+      <c r="E138" s="11"/>
+      <c r="F138" s="11"/>
+      <c r="G138" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" s="11"/>
+      <c r="I138" s="21">
         <v>45839</v>
       </c>
     </row>
     <row r="139" spans="1:9">
-      <c r="A139" s="8">
+      <c r="A139" s="11">
         <v>136</v>
       </c>
-      <c r="B139" s="14"/>
-      <c r="C139" s="17"/>
-      <c r="D139" s="17" t="s">
+      <c r="B139" s="17"/>
+      <c r="C139" s="20"/>
+      <c r="D139" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="E139" s="8"/>
-      <c r="F139" s="8"/>
-      <c r="G139" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H139" s="8"/>
-      <c r="I139" s="18">
+      <c r="E139" s="11"/>
+      <c r="F139" s="11"/>
+      <c r="G139" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" s="11"/>
+      <c r="I139" s="21">
         <v>46054</v>
       </c>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="8">
+      <c r="A140" s="11">
         <v>137</v>
       </c>
-      <c r="B140" s="14"/>
-      <c r="C140" s="17"/>
-      <c r="D140" s="17" t="s">
+      <c r="B140" s="17"/>
+      <c r="C140" s="20"/>
+      <c r="D140" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="E140" s="8"/>
-      <c r="F140" s="8"/>
-      <c r="G140" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H140" s="8"/>
-      <c r="I140" s="18">
+      <c r="E140" s="11"/>
+      <c r="F140" s="11"/>
+      <c r="G140" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" s="11"/>
+      <c r="I140" s="21">
         <v>45839</v>
       </c>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="8">
+      <c r="A141" s="11">
         <v>138</v>
       </c>
-      <c r="B141" s="14"/>
-      <c r="C141" s="17"/>
-      <c r="D141" s="17" t="s">
+      <c r="B141" s="17"/>
+      <c r="C141" s="20"/>
+      <c r="D141" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="E141" s="8"/>
-      <c r="F141" s="8"/>
-      <c r="G141" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H141" s="8"/>
-      <c r="I141" s="18">
+      <c r="E141" s="11"/>
+      <c r="F141" s="11"/>
+      <c r="G141" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" s="11"/>
+      <c r="I141" s="21">
         <v>45839</v>
       </c>
     </row>
     <row r="142" spans="1:9">
-      <c r="A142" s="8">
+      <c r="A142" s="11">
         <v>139</v>
       </c>
-      <c r="B142" s="14"/>
-      <c r="C142" s="17"/>
-      <c r="D142" s="17" t="s">
+      <c r="B142" s="17"/>
+      <c r="C142" s="20"/>
+      <c r="D142" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
-      <c r="G142" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H142" s="8"/>
-      <c r="I142" s="18">
+      <c r="E142" s="11"/>
+      <c r="F142" s="11"/>
+      <c r="G142" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" s="11"/>
+      <c r="I142" s="21">
         <v>45839</v>
       </c>
     </row>
     <row r="143" spans="1:9">
-      <c r="A143" s="8">
+      <c r="A143" s="11">
         <v>140</v>
       </c>
-      <c r="B143" s="14"/>
-      <c r="C143" s="17"/>
-      <c r="D143" s="17" t="s">
+      <c r="B143" s="17"/>
+      <c r="C143" s="20"/>
+      <c r="D143" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8"/>
-      <c r="G143" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H143" s="8"/>
-      <c r="I143" s="18">
+      <c r="E143" s="11"/>
+      <c r="F143" s="11"/>
+      <c r="G143" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" s="11"/>
+      <c r="I143" s="21">
         <v>45839</v>
       </c>
     </row>
     <row r="144" spans="1:9">
-      <c r="A144" s="8">
+      <c r="A144" s="11">
         <v>141</v>
       </c>
-      <c r="B144" s="14"/>
-      <c r="C144" s="17"/>
-      <c r="D144" s="17" t="s">
+      <c r="B144" s="17"/>
+      <c r="C144" s="20"/>
+      <c r="D144" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
-      <c r="G144" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H144" s="8"/>
-      <c r="I144" s="21">
+      <c r="E144" s="11"/>
+      <c r="F144" s="11"/>
+      <c r="G144" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" s="11"/>
+      <c r="I144" s="24">
         <v>45859</v>
       </c>
     </row>
     <row r="145" spans="1:9">
-      <c r="A145" s="8">
+      <c r="A145" s="11">
         <v>142</v>
       </c>
-      <c r="B145" s="14"/>
-      <c r="C145" s="17" t="s">
+      <c r="B145" s="17"/>
+      <c r="C145" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D145" s="17" t="s">
+      <c r="D145" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8"/>
-      <c r="G145" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H145" s="8"/>
-      <c r="I145" s="21"/>
+      <c r="E145" s="11"/>
+      <c r="F145" s="11"/>
+      <c r="G145" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" s="11"/>
+      <c r="I145" s="24"/>
     </row>
     <row r="146" spans="1:9">
-      <c r="A146" s="8">
+      <c r="A146" s="11">
         <v>143</v>
       </c>
-      <c r="B146" s="14"/>
-      <c r="C146" s="17"/>
-      <c r="D146" s="17" t="s">
+      <c r="B146" s="17"/>
+      <c r="C146" s="20"/>
+      <c r="D146" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
-      <c r="G146" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H146" s="8"/>
-      <c r="I146" s="21"/>
+      <c r="E146" s="11"/>
+      <c r="F146" s="11"/>
+      <c r="G146" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" s="11"/>
+      <c r="I146" s="24"/>
     </row>
     <row r="147" spans="1:9">
-      <c r="A147" s="8">
+      <c r="A147" s="11">
         <v>144</v>
       </c>
-      <c r="B147" s="14"/>
-      <c r="C147" s="17"/>
-      <c r="D147" s="17" t="s">
+      <c r="B147" s="17"/>
+      <c r="C147" s="20"/>
+      <c r="D147" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="E147" s="8"/>
-      <c r="F147" s="8"/>
-      <c r="G147" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H147" s="8"/>
-      <c r="I147" s="21"/>
+      <c r="E147" s="11"/>
+      <c r="F147" s="11"/>
+      <c r="G147" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H147" s="11"/>
+      <c r="I147" s="24"/>
     </row>
     <row r="148" spans="1:9">
-      <c r="A148" s="8">
+      <c r="A148" s="11">
         <v>145</v>
       </c>
-      <c r="B148" s="14"/>
-      <c r="C148" s="17"/>
-      <c r="D148" s="17" t="s">
+      <c r="B148" s="17"/>
+      <c r="C148" s="20"/>
+      <c r="D148" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="E148" s="8"/>
-      <c r="F148" s="8"/>
-      <c r="G148" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H148" s="8"/>
-      <c r="I148" s="21"/>
+      <c r="E148" s="11"/>
+      <c r="F148" s="11"/>
+      <c r="G148" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" s="11"/>
+      <c r="I148" s="24"/>
     </row>
     <row r="149" spans="1:9">
-      <c r="A149" s="8">
+      <c r="A149" s="11">
         <v>146</v>
       </c>
-      <c r="B149" s="14"/>
-      <c r="C149" s="17" t="s">
+      <c r="B149" s="17"/>
+      <c r="C149" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D149" s="17" t="s">
+      <c r="D149" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="E149" s="8"/>
-      <c r="F149" s="8"/>
-      <c r="G149" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H149" s="8"/>
-      <c r="I149" s="21"/>
+      <c r="E149" s="11"/>
+      <c r="F149" s="11"/>
+      <c r="G149" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" s="11"/>
+      <c r="I149" s="24"/>
     </row>
     <row r="150" spans="1:9">
-      <c r="A150" s="8">
+      <c r="A150" s="11">
         <v>147</v>
       </c>
-      <c r="B150" s="14"/>
-      <c r="C150" s="17"/>
-      <c r="D150" s="17" t="s">
+      <c r="B150" s="17"/>
+      <c r="C150" s="20"/>
+      <c r="D150" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="E150" s="8"/>
-      <c r="F150" s="8"/>
-      <c r="G150" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H150" s="8"/>
-      <c r="I150" s="21"/>
+      <c r="E150" s="11"/>
+      <c r="F150" s="11"/>
+      <c r="G150" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" s="11"/>
+      <c r="I150" s="24"/>
     </row>
     <row r="151" spans="1:9">
-      <c r="A151" s="8">
+      <c r="A151" s="11">
         <v>148</v>
       </c>
-      <c r="B151" s="14"/>
-      <c r="C151" s="17"/>
-      <c r="D151" s="17" t="s">
+      <c r="B151" s="17"/>
+      <c r="C151" s="20"/>
+      <c r="D151" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="E151" s="8"/>
-      <c r="F151" s="8"/>
-      <c r="G151" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H151" s="8"/>
-      <c r="I151" s="21"/>
+      <c r="E151" s="11"/>
+      <c r="F151" s="11"/>
+      <c r="G151" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" s="11"/>
+      <c r="I151" s="24"/>
     </row>
     <row r="152" spans="1:9">
-      <c r="A152" s="8">
+      <c r="A152" s="11">
         <v>149</v>
       </c>
-      <c r="B152" s="14"/>
-      <c r="C152" s="17"/>
-      <c r="D152" s="17" t="s">
+      <c r="B152" s="17"/>
+      <c r="C152" s="20"/>
+      <c r="D152" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="E152" s="8"/>
-      <c r="F152" s="8"/>
-      <c r="G152" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H152" s="8"/>
-      <c r="I152" s="21"/>
+      <c r="E152" s="11"/>
+      <c r="F152" s="11"/>
+      <c r="G152" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" s="11"/>
+      <c r="I152" s="24"/>
     </row>
     <row r="153" spans="1:9">
-      <c r="A153" s="8">
+      <c r="A153" s="11">
         <v>150</v>
       </c>
-      <c r="B153" s="14"/>
-      <c r="C153" s="17"/>
-      <c r="D153" s="17" t="s">
+      <c r="B153" s="17"/>
+      <c r="C153" s="20"/>
+      <c r="D153" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="E153" s="8"/>
-      <c r="F153" s="8"/>
-      <c r="G153" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H153" s="8"/>
-      <c r="I153" s="21"/>
+      <c r="E153" s="11"/>
+      <c r="F153" s="11"/>
+      <c r="G153" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" s="11"/>
+      <c r="I153" s="24"/>
     </row>
     <row r="154" spans="1:9">
-      <c r="A154" s="8">
+      <c r="A154" s="11">
         <v>151</v>
       </c>
-      <c r="B154" s="14"/>
-      <c r="C154" s="17"/>
-      <c r="D154" s="17" t="s">
+      <c r="B154" s="17"/>
+      <c r="C154" s="20"/>
+      <c r="D154" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="E154" s="8"/>
-      <c r="F154" s="8"/>
-      <c r="G154" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H154" s="8"/>
-      <c r="I154" s="21"/>
+      <c r="E154" s="11"/>
+      <c r="F154" s="11"/>
+      <c r="G154" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" s="11"/>
+      <c r="I154" s="24"/>
     </row>
     <row r="155" spans="1:9">
-      <c r="A155" s="8">
+      <c r="A155" s="11">
         <v>152</v>
       </c>
-      <c r="B155" s="14"/>
-      <c r="C155" s="17"/>
-      <c r="D155" s="17" t="s">
+      <c r="B155" s="17"/>
+      <c r="C155" s="20"/>
+      <c r="D155" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="E155" s="8"/>
-      <c r="F155" s="8"/>
-      <c r="G155" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H155" s="8"/>
-      <c r="I155" s="21"/>
+      <c r="E155" s="11"/>
+      <c r="F155" s="11"/>
+      <c r="G155" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" s="11"/>
+      <c r="I155" s="24"/>
     </row>
     <row r="156" spans="1:9">
-      <c r="A156" s="8">
+      <c r="A156" s="11">
         <v>153</v>
       </c>
-      <c r="B156" s="14"/>
-      <c r="C156" s="17"/>
-      <c r="D156" s="17" t="s">
+      <c r="B156" s="17"/>
+      <c r="C156" s="20"/>
+      <c r="D156" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="E156" s="8"/>
-      <c r="F156" s="8"/>
-      <c r="G156" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H156" s="8"/>
-      <c r="I156" s="21"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
+      <c r="G156" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" s="11"/>
+      <c r="I156" s="24"/>
     </row>
     <row r="157" spans="1:9">
-      <c r="A157" s="8">
+      <c r="A157" s="11">
         <v>154</v>
       </c>
-      <c r="B157" s="14"/>
-      <c r="C157" s="17"/>
-      <c r="D157" s="17" t="s">
+      <c r="B157" s="17"/>
+      <c r="C157" s="20"/>
+      <c r="D157" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="E157" s="8"/>
-      <c r="F157" s="8"/>
-      <c r="G157" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H157" s="8"/>
-      <c r="I157" s="21"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="11"/>
+      <c r="G157" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" s="11"/>
+      <c r="I157" s="24"/>
     </row>
     <row r="158" spans="1:9">
-      <c r="A158" s="8">
+      <c r="A158" s="11">
         <v>155</v>
       </c>
-      <c r="B158" s="14"/>
-      <c r="C158" s="17"/>
-      <c r="D158" s="17" t="s">
+      <c r="B158" s="17"/>
+      <c r="C158" s="20"/>
+      <c r="D158" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="E158" s="8"/>
-      <c r="F158" s="8"/>
-      <c r="G158" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H158" s="8"/>
-      <c r="I158" s="21"/>
+      <c r="E158" s="11"/>
+      <c r="F158" s="11"/>
+      <c r="G158" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" s="11"/>
+      <c r="I158" s="24"/>
     </row>
     <row r="159" spans="1:9">
-      <c r="A159" s="8">
+      <c r="A159" s="11">
         <v>156</v>
       </c>
-      <c r="B159" s="14"/>
-      <c r="C159" s="17"/>
-      <c r="D159" s="17" t="s">
+      <c r="B159" s="17"/>
+      <c r="C159" s="20"/>
+      <c r="D159" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="E159" s="8"/>
-      <c r="F159" s="8"/>
-      <c r="G159" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H159" s="8"/>
-      <c r="I159" s="21"/>
+      <c r="E159" s="11"/>
+      <c r="F159" s="11"/>
+      <c r="G159" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" s="11"/>
+      <c r="I159" s="24"/>
     </row>
     <row r="160" spans="1:9">
-      <c r="A160" s="8">
+      <c r="A160" s="11">
         <v>157</v>
       </c>
-      <c r="B160" s="14"/>
-      <c r="C160" s="17"/>
-      <c r="D160" s="17" t="s">
+      <c r="B160" s="17"/>
+      <c r="C160" s="20"/>
+      <c r="D160" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="E160" s="8"/>
-      <c r="F160" s="8"/>
-      <c r="G160" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H160" s="8"/>
-      <c r="I160" s="21"/>
+      <c r="E160" s="11"/>
+      <c r="F160" s="11"/>
+      <c r="G160" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H160" s="11"/>
+      <c r="I160" s="24"/>
     </row>
     <row r="161" spans="1:9">
-      <c r="A161" s="8">
+      <c r="A161" s="11">
         <v>158</v>
       </c>
-      <c r="B161" s="14"/>
-      <c r="C161" s="17"/>
-      <c r="D161" s="17" t="s">
+      <c r="B161" s="17"/>
+      <c r="C161" s="20"/>
+      <c r="D161" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="E161" s="8"/>
-      <c r="F161" s="8"/>
-      <c r="G161" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H161" s="8"/>
-      <c r="I161" s="21"/>
+      <c r="E161" s="11"/>
+      <c r="F161" s="11"/>
+      <c r="G161" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H161" s="11"/>
+      <c r="I161" s="24"/>
     </row>
     <row r="162" spans="1:9">
-      <c r="A162" s="8">
+      <c r="A162" s="11">
         <v>159</v>
       </c>
-      <c r="B162" s="14"/>
-      <c r="C162" s="17"/>
-      <c r="D162" s="17" t="s">
+      <c r="B162" s="17"/>
+      <c r="C162" s="20"/>
+      <c r="D162" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="E162" s="8"/>
-      <c r="F162" s="8"/>
-      <c r="G162" s="9"/>
-      <c r="H162" s="8"/>
-      <c r="I162" s="21"/>
+      <c r="E162" s="11"/>
+      <c r="F162" s="11"/>
+      <c r="G162" s="12"/>
+      <c r="H162" s="11"/>
+      <c r="I162" s="24"/>
     </row>
     <row r="163" spans="1:9">
-      <c r="A163" s="8">
+      <c r="A163" s="11">
         <v>160</v>
       </c>
-      <c r="B163" s="14"/>
-      <c r="C163" s="17"/>
-      <c r="D163" s="17" t="s">
+      <c r="B163" s="17"/>
+      <c r="C163" s="20"/>
+      <c r="D163" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="E163" s="8"/>
-      <c r="F163" s="8"/>
-      <c r="G163" s="9"/>
-      <c r="H163" s="8"/>
-      <c r="I163" s="21"/>
+      <c r="E163" s="11"/>
+      <c r="F163" s="11"/>
+      <c r="G163" s="12"/>
+      <c r="H163" s="11"/>
+      <c r="I163" s="24"/>
     </row>
     <row r="164" spans="1:9">
-      <c r="A164" s="8">
+      <c r="A164" s="11">
         <v>161</v>
       </c>
-      <c r="B164" s="14"/>
-      <c r="C164" s="17"/>
-      <c r="D164" s="17" t="s">
+      <c r="B164" s="17"/>
+      <c r="C164" s="20"/>
+      <c r="D164" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="E164" s="8"/>
-      <c r="F164" s="8"/>
-      <c r="G164" s="9"/>
-      <c r="H164" s="8"/>
-      <c r="I164" s="21"/>
+      <c r="E164" s="11"/>
+      <c r="F164" s="11"/>
+      <c r="G164" s="12"/>
+      <c r="H164" s="11"/>
+      <c r="I164" s="24"/>
     </row>
     <row r="165" spans="1:9">
-      <c r="A165" s="8">
+      <c r="A165" s="11">
         <v>162</v>
       </c>
-      <c r="B165" s="14"/>
-      <c r="C165" s="17"/>
-      <c r="D165" s="17" t="s">
+      <c r="B165" s="17"/>
+      <c r="C165" s="20"/>
+      <c r="D165" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="E165" s="8"/>
-      <c r="F165" s="8"/>
-      <c r="G165" s="9"/>
-      <c r="H165" s="8"/>
-      <c r="I165" s="21"/>
+      <c r="E165" s="11"/>
+      <c r="F165" s="11"/>
+      <c r="G165" s="12"/>
+      <c r="H165" s="11"/>
+      <c r="I165" s="24"/>
     </row>
     <row r="166" spans="1:9">
-      <c r="A166" s="8">
+      <c r="A166" s="11">
         <v>163</v>
       </c>
-      <c r="B166" s="14"/>
-      <c r="C166" s="17"/>
-      <c r="D166" s="17" t="s">
+      <c r="B166" s="17"/>
+      <c r="C166" s="20"/>
+      <c r="D166" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="E166" s="8"/>
-      <c r="F166" s="8"/>
-      <c r="G166" s="9"/>
-      <c r="H166" s="8"/>
-      <c r="I166" s="21"/>
+      <c r="E166" s="11"/>
+      <c r="F166" s="11"/>
+      <c r="G166" s="12"/>
+      <c r="H166" s="11"/>
+      <c r="I166" s="24"/>
     </row>
     <row r="167" spans="1:9">
-      <c r="A167" s="8">
+      <c r="A167" s="11">
         <v>164</v>
       </c>
-      <c r="B167" s="14"/>
-      <c r="C167" s="17"/>
-      <c r="D167" s="17" t="s">
+      <c r="B167" s="17"/>
+      <c r="C167" s="20"/>
+      <c r="D167" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="E167" s="8"/>
-      <c r="F167" s="8"/>
-      <c r="G167" s="9"/>
-      <c r="H167" s="8"/>
-      <c r="I167" s="21"/>
+      <c r="E167" s="11"/>
+      <c r="F167" s="11"/>
+      <c r="G167" s="12"/>
+      <c r="H167" s="11"/>
+      <c r="I167" s="24"/>
     </row>
     <row r="168" spans="1:9">
-      <c r="A168" s="8">
+      <c r="A168" s="11">
         <v>165</v>
       </c>
-      <c r="B168" s="14"/>
-      <c r="C168" s="17"/>
-      <c r="D168" s="17" t="s">
+      <c r="B168" s="17"/>
+      <c r="C168" s="20"/>
+      <c r="D168" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="E168" s="8"/>
-      <c r="F168" s="8"/>
-      <c r="G168" s="9"/>
-      <c r="H168" s="8"/>
-      <c r="I168" s="21"/>
+      <c r="E168" s="11"/>
+      <c r="F168" s="11"/>
+      <c r="G168" s="12"/>
+      <c r="H168" s="11"/>
+      <c r="I168" s="24"/>
     </row>
     <row r="169" spans="1:9">
-      <c r="A169" s="8">
+      <c r="A169" s="11">
         <v>166</v>
       </c>
-      <c r="B169" s="14"/>
-      <c r="C169" s="17"/>
-      <c r="D169" s="17" t="s">
+      <c r="B169" s="17"/>
+      <c r="C169" s="20"/>
+      <c r="D169" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="E169" s="8"/>
-      <c r="F169" s="8"/>
-      <c r="G169" s="9"/>
-      <c r="H169" s="8"/>
-      <c r="I169" s="21"/>
+      <c r="E169" s="11"/>
+      <c r="F169" s="11"/>
+      <c r="G169" s="12"/>
+      <c r="H169" s="11"/>
+      <c r="I169" s="24"/>
     </row>
     <row r="170" spans="1:9">
-      <c r="A170" s="8">
+      <c r="A170" s="11">
         <v>167</v>
       </c>
-      <c r="B170" s="14"/>
-      <c r="C170" s="17"/>
-      <c r="D170" s="17" t="s">
+      <c r="B170" s="17"/>
+      <c r="C170" s="20"/>
+      <c r="D170" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="E170" s="8"/>
-      <c r="F170" s="8"/>
-      <c r="G170" s="9"/>
-      <c r="H170" s="8"/>
-      <c r="I170" s="21"/>
+      <c r="E170" s="11"/>
+      <c r="F170" s="11"/>
+      <c r="G170" s="12"/>
+      <c r="H170" s="11"/>
+      <c r="I170" s="24"/>
     </row>
     <row r="171" spans="1:9">
-      <c r="A171" s="8">
+      <c r="A171" s="11">
         <v>168</v>
       </c>
-      <c r="B171" s="14"/>
-      <c r="C171" s="17"/>
-      <c r="D171" s="17" t="s">
+      <c r="B171" s="17"/>
+      <c r="C171" s="20"/>
+      <c r="D171" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="E171" s="8"/>
-      <c r="F171" s="8"/>
-      <c r="G171" s="9"/>
-      <c r="H171" s="8"/>
-      <c r="I171" s="21"/>
+      <c r="E171" s="11"/>
+      <c r="F171" s="11"/>
+      <c r="G171" s="12"/>
+      <c r="H171" s="11"/>
+      <c r="I171" s="24"/>
     </row>
     <row r="172" spans="1:9">
-      <c r="A172" s="8">
+      <c r="A172" s="11">
         <v>169</v>
       </c>
-      <c r="B172" s="14"/>
-      <c r="C172" s="17"/>
-      <c r="D172" s="17" t="s">
+      <c r="B172" s="17"/>
+      <c r="C172" s="20"/>
+      <c r="D172" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="E172" s="8"/>
-      <c r="F172" s="8"/>
-      <c r="G172" s="9"/>
-      <c r="H172" s="8"/>
-      <c r="I172" s="21"/>
+      <c r="E172" s="11"/>
+      <c r="F172" s="11"/>
+      <c r="G172" s="12"/>
+      <c r="H172" s="11"/>
+      <c r="I172" s="24"/>
     </row>
     <row r="173" spans="1:9">
-      <c r="A173" s="8">
+      <c r="A173" s="11">
         <v>170</v>
       </c>
-      <c r="B173" s="14"/>
-      <c r="C173" s="17"/>
-      <c r="D173" s="17" t="s">
+      <c r="B173" s="17"/>
+      <c r="C173" s="20"/>
+      <c r="D173" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="E173" s="8"/>
-      <c r="F173" s="8"/>
-      <c r="G173" s="9"/>
-      <c r="H173" s="8"/>
-      <c r="I173" s="21"/>
+      <c r="E173" s="11"/>
+      <c r="F173" s="11"/>
+      <c r="G173" s="12"/>
+      <c r="H173" s="11"/>
+      <c r="I173" s="24"/>
     </row>
     <row r="174" spans="1:9">
-      <c r="A174" s="8">
+      <c r="A174" s="11">
         <v>171</v>
       </c>
-      <c r="B174" s="14"/>
-      <c r="C174" s="17"/>
-      <c r="D174" s="17" t="s">
+      <c r="B174" s="17"/>
+      <c r="C174" s="20"/>
+      <c r="D174" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="E174" s="8"/>
-      <c r="F174" s="8"/>
-      <c r="G174" s="9"/>
-      <c r="H174" s="8"/>
-      <c r="I174" s="21"/>
+      <c r="E174" s="11"/>
+      <c r="F174" s="11"/>
+      <c r="G174" s="12"/>
+      <c r="H174" s="11"/>
+      <c r="I174" s="24"/>
     </row>
     <row r="175" spans="1:9">
-      <c r="A175" s="8">
+      <c r="A175" s="11">
         <v>172</v>
       </c>
-      <c r="B175" s="14"/>
-      <c r="C175" s="17"/>
-      <c r="D175" s="17" t="s">
+      <c r="B175" s="17"/>
+      <c r="C175" s="20"/>
+      <c r="D175" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="E175" s="8"/>
-      <c r="F175" s="8"/>
-      <c r="G175" s="9"/>
-      <c r="H175" s="8"/>
-      <c r="I175" s="21"/>
+      <c r="E175" s="11"/>
+      <c r="F175" s="11"/>
+      <c r="G175" s="12"/>
+      <c r="H175" s="11"/>
+      <c r="I175" s="24"/>
     </row>
     <row r="176" spans="1:9">
-      <c r="A176" s="8">
+      <c r="A176" s="11">
         <v>173</v>
       </c>
-      <c r="B176" s="14"/>
-      <c r="C176" s="17"/>
-      <c r="D176" s="17" t="s">
+      <c r="B176" s="17"/>
+      <c r="C176" s="20"/>
+      <c r="D176" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="E176" s="8"/>
-      <c r="F176" s="8"/>
-      <c r="G176" s="9"/>
-      <c r="H176" s="8"/>
-      <c r="I176" s="21"/>
+      <c r="E176" s="11"/>
+      <c r="F176" s="11"/>
+      <c r="G176" s="12"/>
+      <c r="H176" s="11"/>
+      <c r="I176" s="24"/>
     </row>
     <row r="177" spans="1:9">
-      <c r="A177" s="8">
+      <c r="A177" s="11">
         <v>174</v>
       </c>
-      <c r="B177" s="14"/>
-      <c r="C177" s="17"/>
-      <c r="D177" s="17" t="s">
+      <c r="B177" s="17"/>
+      <c r="C177" s="20"/>
+      <c r="D177" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="E177" s="8"/>
-      <c r="F177" s="8"/>
-      <c r="G177" s="9"/>
-      <c r="H177" s="8"/>
-      <c r="I177" s="21"/>
+      <c r="E177" s="11"/>
+      <c r="F177" s="11"/>
+      <c r="G177" s="12"/>
+      <c r="H177" s="11"/>
+      <c r="I177" s="24"/>
     </row>
     <row r="178" spans="1:9">
-      <c r="A178" s="8">
+      <c r="A178" s="11">
         <v>175</v>
       </c>
-      <c r="B178" s="14"/>
-      <c r="C178" s="17"/>
-      <c r="D178" s="17" t="s">
+      <c r="B178" s="17"/>
+      <c r="C178" s="20"/>
+      <c r="D178" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="E178" s="8"/>
-      <c r="F178" s="8"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="8"/>
-      <c r="I178" s="21"/>
+      <c r="E178" s="11"/>
+      <c r="F178" s="11"/>
+      <c r="G178" s="12"/>
+      <c r="H178" s="11"/>
+      <c r="I178" s="24"/>
     </row>
     <row r="179" spans="1:9">
-      <c r="A179" s="8">
+      <c r="A179" s="11">
         <v>176</v>
       </c>
-      <c r="B179" s="14"/>
-      <c r="C179" s="17"/>
-      <c r="D179" s="17" t="s">
+      <c r="B179" s="17"/>
+      <c r="C179" s="20"/>
+      <c r="D179" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="E179" s="8"/>
-      <c r="F179" s="8"/>
-      <c r="G179" s="9"/>
-      <c r="H179" s="8"/>
-      <c r="I179" s="21"/>
+      <c r="E179" s="11"/>
+      <c r="F179" s="11"/>
+      <c r="G179" s="12"/>
+      <c r="H179" s="11"/>
+      <c r="I179" s="24"/>
     </row>
     <row r="180" spans="1:9">
-      <c r="A180" s="8">
+      <c r="A180" s="11">
         <v>177</v>
       </c>
-      <c r="B180" s="14"/>
-      <c r="C180" s="17"/>
-      <c r="D180" s="17" t="s">
+      <c r="B180" s="17"/>
+      <c r="C180" s="20"/>
+      <c r="D180" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="E180" s="8"/>
-      <c r="F180" s="8"/>
-      <c r="G180" s="9"/>
-      <c r="H180" s="8"/>
-      <c r="I180" s="21"/>
+      <c r="E180" s="11"/>
+      <c r="F180" s="11"/>
+      <c r="G180" s="12"/>
+      <c r="H180" s="11"/>
+      <c r="I180" s="24"/>
     </row>
     <row r="181" spans="1:9">
-      <c r="A181" s="8">
+      <c r="A181" s="11">
         <v>178</v>
       </c>
-      <c r="B181" s="14"/>
-      <c r="C181" s="17"/>
-      <c r="D181" s="17" t="s">
+      <c r="B181" s="17"/>
+      <c r="C181" s="20"/>
+      <c r="D181" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="E181" s="8"/>
-      <c r="F181" s="8"/>
-      <c r="G181" s="9"/>
-      <c r="H181" s="8"/>
-      <c r="I181" s="21"/>
+      <c r="E181" s="11"/>
+      <c r="F181" s="11"/>
+      <c r="G181" s="12"/>
+      <c r="H181" s="11"/>
+      <c r="I181" s="24"/>
     </row>
     <row r="182" spans="1:9">
-      <c r="A182" s="8">
+      <c r="A182" s="11">
         <v>179</v>
       </c>
-      <c r="B182" s="14"/>
-      <c r="C182" s="17"/>
-      <c r="D182" s="17" t="s">
+      <c r="B182" s="17"/>
+      <c r="C182" s="20"/>
+      <c r="D182" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="E182" s="8"/>
-      <c r="F182" s="8"/>
-      <c r="G182" s="9"/>
-      <c r="H182" s="8"/>
-      <c r="I182" s="21"/>
+      <c r="E182" s="11"/>
+      <c r="F182" s="11"/>
+      <c r="G182" s="12"/>
+      <c r="H182" s="11"/>
+      <c r="I182" s="24"/>
     </row>
     <row r="183" spans="1:9">
-      <c r="A183" s="8">
+      <c r="A183" s="11">
         <v>180</v>
       </c>
-      <c r="B183" s="14"/>
-      <c r="C183" s="17"/>
-      <c r="D183" s="17" t="s">
+      <c r="B183" s="17"/>
+      <c r="C183" s="20"/>
+      <c r="D183" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="E183" s="8"/>
-      <c r="F183" s="8"/>
-      <c r="G183" s="9"/>
-      <c r="H183" s="8"/>
-      <c r="I183" s="21"/>
+      <c r="E183" s="11"/>
+      <c r="F183" s="11"/>
+      <c r="G183" s="12"/>
+      <c r="H183" s="11"/>
+      <c r="I183" s="24"/>
     </row>
     <row r="184" spans="1:9">
-      <c r="A184" s="8">
+      <c r="A184" s="11">
         <v>181</v>
       </c>
-      <c r="B184" s="14"/>
-      <c r="C184" s="17"/>
-      <c r="D184" s="17" t="s">
+      <c r="B184" s="17"/>
+      <c r="C184" s="20"/>
+      <c r="D184" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="E184" s="8"/>
-      <c r="F184" s="8"/>
-      <c r="G184" s="9"/>
-      <c r="H184" s="8"/>
-      <c r="I184" s="21"/>
+      <c r="E184" s="11"/>
+      <c r="F184" s="11"/>
+      <c r="G184" s="12"/>
+      <c r="H184" s="11"/>
+      <c r="I184" s="24"/>
     </row>
     <row r="185" spans="1:9">
-      <c r="A185" s="8">
+      <c r="A185" s="11">
         <v>182</v>
       </c>
-      <c r="B185" s="14"/>
-      <c r="C185" s="17"/>
-      <c r="D185" s="17" t="s">
+      <c r="B185" s="17"/>
+      <c r="C185" s="20"/>
+      <c r="D185" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="E185" s="8"/>
-      <c r="F185" s="8"/>
-      <c r="G185" s="9"/>
-      <c r="H185" s="8"/>
-      <c r="I185" s="21"/>
+      <c r="E185" s="11"/>
+      <c r="F185" s="11"/>
+      <c r="G185" s="12"/>
+      <c r="H185" s="11"/>
+      <c r="I185" s="24"/>
     </row>
     <row r="186" spans="1:9">
-      <c r="A186" s="8">
+      <c r="A186" s="11">
         <v>183</v>
       </c>
-      <c r="B186" s="14"/>
-      <c r="C186" s="17"/>
-      <c r="D186" s="17" t="s">
+      <c r="B186" s="17"/>
+      <c r="C186" s="20"/>
+      <c r="D186" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="E186" s="8"/>
-      <c r="F186" s="8"/>
-      <c r="G186" s="9"/>
-      <c r="H186" s="8"/>
-      <c r="I186" s="21"/>
+      <c r="E186" s="11"/>
+      <c r="F186" s="11"/>
+      <c r="G186" s="12"/>
+      <c r="H186" s="11"/>
+      <c r="I186" s="24"/>
     </row>
     <row r="187" spans="1:9">
-      <c r="A187" s="8">
+      <c r="A187" s="11">
         <v>184</v>
       </c>
-      <c r="B187" s="14"/>
-      <c r="C187" s="17"/>
-      <c r="D187" s="17" t="s">
+      <c r="B187" s="17"/>
+      <c r="C187" s="20"/>
+      <c r="D187" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="E187" s="8"/>
-      <c r="F187" s="8"/>
-      <c r="G187" s="9"/>
-      <c r="H187" s="8"/>
-      <c r="I187" s="21"/>
+      <c r="E187" s="11"/>
+      <c r="F187" s="11"/>
+      <c r="G187" s="12"/>
+      <c r="H187" s="11"/>
+      <c r="I187" s="24"/>
     </row>
     <row r="188" spans="1:9">
-      <c r="A188" s="8">
+      <c r="A188" s="11">
         <v>185</v>
       </c>
-      <c r="B188" s="14"/>
-      <c r="C188" s="17"/>
-      <c r="D188" s="17" t="s">
+      <c r="B188" s="17"/>
+      <c r="C188" s="20"/>
+      <c r="D188" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="E188" s="8"/>
-      <c r="F188" s="8"/>
-      <c r="G188" s="9"/>
-      <c r="H188" s="8"/>
-      <c r="I188" s="21"/>
+      <c r="E188" s="11"/>
+      <c r="F188" s="11"/>
+      <c r="G188" s="12"/>
+      <c r="H188" s="11"/>
+      <c r="I188" s="24"/>
     </row>
     <row r="189" spans="1:9">
-      <c r="A189" s="8">
+      <c r="A189" s="11">
         <v>186</v>
       </c>
-      <c r="B189" s="14"/>
-      <c r="C189" s="17"/>
-      <c r="D189" s="17" t="s">
+      <c r="B189" s="17"/>
+      <c r="C189" s="20"/>
+      <c r="D189" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E189" s="8"/>
-      <c r="F189" s="8"/>
-      <c r="G189" s="9"/>
-      <c r="H189" s="8"/>
-      <c r="I189" s="21"/>
+      <c r="E189" s="11"/>
+      <c r="F189" s="11"/>
+      <c r="G189" s="12"/>
+      <c r="H189" s="11"/>
+      <c r="I189" s="24"/>
     </row>
     <row r="190" spans="1:9">
-      <c r="A190" s="8">
+      <c r="A190" s="11">
         <v>187</v>
       </c>
-      <c r="B190" s="14"/>
-      <c r="C190" s="17"/>
-      <c r="D190" s="17" t="s">
+      <c r="B190" s="17"/>
+      <c r="C190" s="20"/>
+      <c r="D190" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="E190" s="8"/>
-      <c r="F190" s="8"/>
-      <c r="G190" s="9"/>
-      <c r="H190" s="8"/>
-      <c r="I190" s="21"/>
+      <c r="E190" s="11"/>
+      <c r="F190" s="11"/>
+      <c r="G190" s="12"/>
+      <c r="H190" s="11"/>
+      <c r="I190" s="24"/>
     </row>
     <row r="191" spans="1:9">
-      <c r="A191" s="8">
+      <c r="A191" s="11">
         <v>188</v>
       </c>
-      <c r="B191" s="14"/>
-      <c r="C191" s="17"/>
-      <c r="D191" s="17" t="s">
+      <c r="B191" s="17"/>
+      <c r="C191" s="20"/>
+      <c r="D191" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="E191" s="8"/>
-      <c r="F191" s="8"/>
-      <c r="G191" s="9"/>
-      <c r="H191" s="8"/>
-      <c r="I191" s="21"/>
+      <c r="E191" s="11"/>
+      <c r="F191" s="11"/>
+      <c r="G191" s="12"/>
+      <c r="H191" s="11"/>
+      <c r="I191" s="24"/>
     </row>
     <row r="192" spans="1:9">
-      <c r="A192" s="8">
+      <c r="A192" s="11">
         <v>189</v>
       </c>
-      <c r="B192" s="14"/>
-      <c r="C192" s="17" t="s">
+      <c r="B192" s="17"/>
+      <c r="C192" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D192" s="17" t="s">
+      <c r="D192" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="E192" s="8"/>
-      <c r="F192" s="8"/>
-      <c r="G192" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H192" s="8"/>
-      <c r="I192" s="21"/>
+      <c r="E192" s="11"/>
+      <c r="F192" s="11"/>
+      <c r="G192" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" s="11"/>
+      <c r="I192" s="24"/>
     </row>
     <row r="193" spans="1:9">
-      <c r="A193" s="8">
+      <c r="A193" s="11">
         <v>190</v>
       </c>
-      <c r="B193" s="14"/>
-      <c r="C193" s="17" t="s">
+      <c r="B193" s="17"/>
+      <c r="C193" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D193" s="17" t="s">
+      <c r="D193" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="E193" s="8"/>
-      <c r="F193" s="8"/>
-      <c r="G193" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H193" s="8"/>
-      <c r="I193" s="21"/>
+      <c r="E193" s="11"/>
+      <c r="F193" s="11"/>
+      <c r="G193" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H193" s="11"/>
+      <c r="I193" s="24"/>
     </row>
     <row r="194" spans="1:9">
-      <c r="A194" s="8">
+      <c r="A194" s="11">
         <v>191</v>
       </c>
-      <c r="B194" s="14"/>
-      <c r="C194" s="17" t="s">
+      <c r="B194" s="17"/>
+      <c r="C194" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D194" s="17" t="s">
+      <c r="D194" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="E194" s="8"/>
-      <c r="F194" s="8"/>
-      <c r="G194" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H194" s="8"/>
-      <c r="I194" s="21"/>
+      <c r="E194" s="11"/>
+      <c r="F194" s="11"/>
+      <c r="G194" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H194" s="11"/>
+      <c r="I194" s="24"/>
     </row>
     <row r="195" spans="1:9">
-      <c r="A195" s="8">
+      <c r="A195" s="11">
         <v>192</v>
       </c>
-      <c r="B195" s="14"/>
-      <c r="C195" s="17" t="s">
+      <c r="B195" s="17"/>
+      <c r="C195" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D195" s="17" t="s">
+      <c r="D195" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="E195" s="8"/>
-      <c r="F195" s="8"/>
-      <c r="G195" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H195" s="8"/>
-      <c r="I195" s="21"/>
+      <c r="E195" s="11"/>
+      <c r="F195" s="11"/>
+      <c r="G195" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H195" s="11"/>
+      <c r="I195" s="24"/>
     </row>
     <row r="196" spans="1:9">
-      <c r="A196" s="8">
+      <c r="A196" s="11">
         <v>193</v>
       </c>
-      <c r="B196" s="14"/>
-      <c r="C196" s="17" t="s">
+      <c r="B196" s="17"/>
+      <c r="C196" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D196" s="17" t="s">
+      <c r="D196" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="E196" s="8"/>
-      <c r="F196" s="8"/>
-      <c r="G196" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H196" s="8"/>
-      <c r="I196" s="21"/>
+      <c r="E196" s="11"/>
+      <c r="F196" s="11"/>
+      <c r="G196" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H196" s="11"/>
+      <c r="I196" s="24"/>
     </row>
     <row r="197" spans="1:9">
-      <c r="A197" s="8">
+      <c r="A197" s="11">
         <v>194</v>
       </c>
-      <c r="B197" s="14"/>
-      <c r="C197" s="17" t="s">
+      <c r="B197" s="17"/>
+      <c r="C197" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D197" s="17" t="s">
+      <c r="D197" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="E197" s="8"/>
-      <c r="F197" s="8"/>
-      <c r="G197" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H197" s="8"/>
-      <c r="I197" s="21"/>
+      <c r="E197" s="11"/>
+      <c r="F197" s="11"/>
+      <c r="G197" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H197" s="11"/>
+      <c r="I197" s="24"/>
     </row>
     <row r="198" spans="1:9">
-      <c r="A198" s="8">
+      <c r="A198" s="11">
         <v>195</v>
       </c>
-      <c r="B198" s="14"/>
-      <c r="C198" s="17" t="s">
+      <c r="B198" s="17"/>
+      <c r="C198" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D198" s="17" t="s">
+      <c r="D198" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="E198" s="8"/>
-      <c r="F198" s="8"/>
-      <c r="G198" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H198" s="8"/>
-      <c r="I198" s="21"/>
+      <c r="E198" s="11"/>
+      <c r="F198" s="11"/>
+      <c r="G198" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H198" s="11"/>
+      <c r="I198" s="24"/>
     </row>
     <row r="199" spans="1:9">
-      <c r="A199" s="8">
+      <c r="A199" s="11">
         <v>196</v>
       </c>
-      <c r="B199" s="14"/>
-      <c r="C199" s="17" t="s">
+      <c r="B199" s="17"/>
+      <c r="C199" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D199" s="17" t="s">
+      <c r="D199" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="E199" s="8"/>
-      <c r="F199" s="8"/>
-      <c r="G199" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H199" s="8"/>
-      <c r="I199" s="21"/>
+      <c r="E199" s="11"/>
+      <c r="F199" s="11"/>
+      <c r="G199" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H199" s="11"/>
+      <c r="I199" s="24"/>
     </row>
     <row r="200" spans="1:9">
-      <c r="A200" s="8">
+      <c r="A200" s="11">
         <v>197</v>
       </c>
-      <c r="B200" s="14"/>
-      <c r="C200" s="17" t="s">
+      <c r="B200" s="17"/>
+      <c r="C200" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D200" s="17" t="s">
+      <c r="D200" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="E200" s="8"/>
-      <c r="F200" s="8"/>
-      <c r="G200" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H200" s="8"/>
-      <c r="I200" s="21"/>
+      <c r="E200" s="11"/>
+      <c r="F200" s="11"/>
+      <c r="G200" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H200" s="11"/>
+      <c r="I200" s="24"/>
     </row>
     <row r="201" spans="1:9">
-      <c r="A201" s="8">
+      <c r="A201" s="11">
         <v>198</v>
       </c>
-      <c r="B201" s="14"/>
-      <c r="C201" s="17" t="s">
+      <c r="B201" s="17"/>
+      <c r="C201" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D201" s="17" t="s">
+      <c r="D201" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="E201" s="8"/>
-      <c r="F201" s="8"/>
-      <c r="G201" s="9"/>
-      <c r="H201" s="8"/>
-      <c r="I201" s="21"/>
+      <c r="E201" s="11"/>
+      <c r="F201" s="11"/>
+      <c r="G201" s="12"/>
+      <c r="H201" s="11"/>
+      <c r="I201" s="24"/>
     </row>
     <row r="202" spans="1:9">
-      <c r="A202" s="8">
+      <c r="A202" s="11">
         <v>199</v>
       </c>
-      <c r="B202" s="14"/>
-      <c r="C202" s="17" t="s">
+      <c r="B202" s="17"/>
+      <c r="C202" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D202" s="17" t="s">
+      <c r="D202" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="E202" s="8"/>
-      <c r="F202" s="8"/>
-      <c r="G202" s="9"/>
-      <c r="H202" s="8"/>
-      <c r="I202" s="21"/>
+      <c r="E202" s="11"/>
+      <c r="F202" s="11"/>
+      <c r="G202" s="12"/>
+      <c r="H202" s="11"/>
+      <c r="I202" s="24"/>
     </row>
     <row r="203" spans="1:9">
-      <c r="A203" s="8">
+      <c r="A203" s="11">
         <v>200</v>
       </c>
-      <c r="B203" s="14"/>
-      <c r="C203" s="17" t="s">
+      <c r="B203" s="17"/>
+      <c r="C203" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D203" s="17" t="s">
+      <c r="D203" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="E203" s="8"/>
-      <c r="F203" s="8"/>
-      <c r="G203" s="9"/>
-      <c r="H203" s="8"/>
-      <c r="I203" s="21"/>
+      <c r="E203" s="11"/>
+      <c r="F203" s="11"/>
+      <c r="G203" s="12"/>
+      <c r="H203" s="11"/>
+      <c r="I203" s="24"/>
     </row>
     <row r="204" spans="1:9">
-      <c r="A204" s="8">
+      <c r="A204" s="11">
         <v>201</v>
       </c>
-      <c r="B204" s="14"/>
-      <c r="C204" s="17" t="s">
+      <c r="B204" s="17"/>
+      <c r="C204" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D204" s="17" t="s">
+      <c r="D204" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="E204" s="8"/>
-      <c r="F204" s="8"/>
-      <c r="G204" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H204" s="8"/>
-      <c r="I204" s="21"/>
+      <c r="E204" s="11"/>
+      <c r="F204" s="11"/>
+      <c r="G204" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H204" s="11"/>
+      <c r="I204" s="24"/>
     </row>
     <row r="205" spans="1:9">
-      <c r="A205" s="8">
+      <c r="A205" s="11">
         <v>202</v>
       </c>
-      <c r="B205" s="14"/>
-      <c r="C205" s="17" t="s">
+      <c r="B205" s="17"/>
+      <c r="C205" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D205" s="17" t="s">
+      <c r="D205" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="E205" s="8"/>
-      <c r="F205" s="8"/>
-      <c r="G205" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H205" s="8"/>
-      <c r="I205" s="21"/>
+      <c r="E205" s="11"/>
+      <c r="F205" s="11"/>
+      <c r="G205" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H205" s="11"/>
+      <c r="I205" s="24"/>
     </row>
     <row r="206" spans="1:9">
-      <c r="A206" s="8">
+      <c r="A206" s="11">
         <v>203</v>
       </c>
-      <c r="B206" s="14"/>
-      <c r="C206" s="17" t="s">
+      <c r="B206" s="17"/>
+      <c r="C206" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D206" s="17" t="s">
+      <c r="D206" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="E206" s="8"/>
-      <c r="F206" s="8"/>
-      <c r="G206" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H206" s="8"/>
-      <c r="I206" s="21"/>
+      <c r="E206" s="11"/>
+      <c r="F206" s="11"/>
+      <c r="G206" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H206" s="11"/>
+      <c r="I206" s="24"/>
     </row>
     <row r="207" spans="1:9">
-      <c r="A207" s="8">
+      <c r="A207" s="11">
         <v>204</v>
       </c>
-      <c r="B207" s="14"/>
-      <c r="C207" s="17" t="s">
+      <c r="B207" s="17"/>
+      <c r="C207" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D207" s="17" t="s">
+      <c r="D207" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="E207" s="8"/>
-      <c r="F207" s="8"/>
-      <c r="G207" s="9"/>
-      <c r="H207" s="8"/>
-      <c r="I207" s="21"/>
+      <c r="E207" s="11"/>
+      <c r="F207" s="11"/>
+      <c r="G207" s="12"/>
+      <c r="H207" s="11"/>
+      <c r="I207" s="24"/>
     </row>
     <row r="208" spans="1:9">
-      <c r="A208" s="8">
+      <c r="A208" s="11">
         <v>205</v>
       </c>
-      <c r="B208" s="14"/>
-      <c r="C208" s="17" t="s">
+      <c r="B208" s="17"/>
+      <c r="C208" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D208" s="17" t="s">
+      <c r="D208" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="E208" s="8"/>
-      <c r="F208" s="8"/>
-      <c r="G208" s="9"/>
-      <c r="H208" s="8"/>
-      <c r="I208" s="21"/>
+      <c r="E208" s="11"/>
+      <c r="F208" s="11"/>
+      <c r="G208" s="12"/>
+      <c r="H208" s="11"/>
+      <c r="I208" s="24"/>
     </row>
     <row r="209" spans="1:9">
-      <c r="A209" s="8">
+      <c r="A209" s="11">
         <v>206</v>
       </c>
-      <c r="B209" s="14"/>
-      <c r="C209" s="17" t="s">
+      <c r="B209" s="17"/>
+      <c r="C209" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D209" s="17" t="s">
+      <c r="D209" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="E209" s="8"/>
-      <c r="F209" s="8"/>
-      <c r="G209" s="9"/>
-      <c r="H209" s="8"/>
-      <c r="I209" s="21"/>
+      <c r="E209" s="11"/>
+      <c r="F209" s="11"/>
+      <c r="G209" s="12"/>
+      <c r="H209" s="11"/>
+      <c r="I209" s="24"/>
     </row>
     <row r="210" spans="1:9">
-      <c r="A210" s="8">
+      <c r="A210" s="11">
         <v>207</v>
       </c>
-      <c r="B210" s="14"/>
-      <c r="C210" s="17" t="s">
+      <c r="B210" s="17"/>
+      <c r="C210" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D210" s="17" t="s">
+      <c r="D210" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="E210" s="8"/>
-      <c r="F210" s="8"/>
-      <c r="G210" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H210" s="8"/>
-      <c r="I210" s="21"/>
+      <c r="E210" s="11"/>
+      <c r="F210" s="11"/>
+      <c r="G210" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H210" s="11"/>
+      <c r="I210" s="24"/>
     </row>
     <row r="211" spans="1:9">
-      <c r="A211" s="8">
+      <c r="A211" s="11">
         <v>208</v>
       </c>
-      <c r="B211" s="14"/>
-      <c r="C211" s="17" t="s">
+      <c r="B211" s="17"/>
+      <c r="C211" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D211" s="17" t="s">
+      <c r="D211" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="E211" s="8"/>
-      <c r="F211" s="8"/>
-      <c r="G211" s="9" t="s">
+      <c r="E211" s="11"/>
+      <c r="F211" s="11"/>
+      <c r="G211" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="H211" s="8"/>
-      <c r="I211" s="21"/>
+      <c r="H211" s="11"/>
+      <c r="I211" s="24"/>
     </row>
     <row r="212" spans="1:9">
-      <c r="A212" s="8">
+      <c r="A212" s="11">
         <v>209</v>
       </c>
-      <c r="B212" s="14"/>
-      <c r="C212" s="17" t="s">
+      <c r="B212" s="17"/>
+      <c r="C212" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D212" s="17" t="s">
+      <c r="D212" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="E212" s="8"/>
-      <c r="F212" s="8"/>
-      <c r="G212" s="9"/>
-      <c r="H212" s="8"/>
-      <c r="I212" s="21"/>
+      <c r="E212" s="11"/>
+      <c r="F212" s="11"/>
+      <c r="G212" s="12"/>
+      <c r="H212" s="11"/>
+      <c r="I212" s="24"/>
     </row>
     <row r="213" spans="1:9">
-      <c r="A213" s="8">
+      <c r="A213" s="11">
         <v>210</v>
       </c>
-      <c r="B213" s="14"/>
-      <c r="C213" s="17" t="s">
+      <c r="B213" s="17"/>
+      <c r="C213" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D213" s="17" t="s">
+      <c r="D213" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="E213" s="8"/>
-      <c r="F213" s="8"/>
-      <c r="G213" s="9"/>
-      <c r="H213" s="8"/>
-      <c r="I213" s="21"/>
+      <c r="E213" s="11"/>
+      <c r="F213" s="11"/>
+      <c r="G213" s="12"/>
+      <c r="H213" s="11"/>
+      <c r="I213" s="24"/>
     </row>
     <row r="214" spans="1:9">
-      <c r="A214" s="8">
+      <c r="A214" s="11">
         <v>211</v>
       </c>
-      <c r="B214" s="14"/>
-      <c r="C214" s="17" t="s">
+      <c r="B214" s="17"/>
+      <c r="C214" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D214" s="17" t="s">
+      <c r="D214" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="E214" s="8"/>
-      <c r="F214" s="8"/>
-      <c r="G214" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H214" s="8"/>
-      <c r="I214" s="21"/>
+      <c r="E214" s="11"/>
+      <c r="F214" s="11"/>
+      <c r="G214" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H214" s="11"/>
+      <c r="I214" s="24"/>
     </row>
     <row r="215" spans="1:9">
-      <c r="A215" s="8">
+      <c r="A215" s="11">
         <v>212</v>
       </c>
-      <c r="B215" s="14"/>
-      <c r="C215" s="17" t="s">
+      <c r="B215" s="17"/>
+      <c r="C215" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D215" s="17" t="s">
+      <c r="D215" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="E215" s="8"/>
-      <c r="F215" s="8"/>
-      <c r="G215" s="9"/>
-      <c r="H215" s="8"/>
-      <c r="I215" s="21"/>
+      <c r="E215" s="11"/>
+      <c r="F215" s="11"/>
+      <c r="G215" s="12"/>
+      <c r="H215" s="11"/>
+      <c r="I215" s="24"/>
     </row>
     <row r="216" spans="1:9">
-      <c r="A216" s="8">
+      <c r="A216" s="11">
         <v>213</v>
       </c>
-      <c r="B216" s="14"/>
-      <c r="C216" s="17" t="s">
+      <c r="B216" s="17"/>
+      <c r="C216" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D216" s="17" t="s">
+      <c r="D216" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="E216" s="8"/>
-      <c r="F216" s="8"/>
-      <c r="G216" s="9"/>
-      <c r="H216" s="8"/>
-      <c r="I216" s="21"/>
+      <c r="E216" s="11"/>
+      <c r="F216" s="11"/>
+      <c r="G216" s="12"/>
+      <c r="H216" s="11"/>
+      <c r="I216" s="24"/>
     </row>
     <row r="217" spans="1:9">
-      <c r="A217" s="8">
+      <c r="A217" s="11">
         <v>214</v>
       </c>
-      <c r="B217" s="14"/>
-      <c r="C217" s="17" t="s">
+      <c r="B217" s="17"/>
+      <c r="C217" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D217" s="17" t="s">
+      <c r="D217" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="E217" s="8"/>
-      <c r="F217" s="8"/>
-      <c r="G217" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H217" s="8"/>
-      <c r="I217" s="21"/>
+      <c r="E217" s="11"/>
+      <c r="F217" s="11"/>
+      <c r="G217" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H217" s="11"/>
+      <c r="I217" s="24"/>
     </row>
     <row r="218" spans="1:9">
-      <c r="A218" s="8">
+      <c r="A218" s="11">
         <v>215</v>
       </c>
-      <c r="B218" s="14"/>
-      <c r="C218" s="17" t="s">
+      <c r="B218" s="17"/>
+      <c r="C218" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D218" s="17" t="s">
+      <c r="D218" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="E218" s="8"/>
-      <c r="F218" s="8"/>
-      <c r="G218" s="9"/>
-      <c r="H218" s="8"/>
-      <c r="I218" s="21"/>
+      <c r="E218" s="11"/>
+      <c r="F218" s="11"/>
+      <c r="G218" s="12"/>
+      <c r="H218" s="11"/>
+      <c r="I218" s="24"/>
     </row>
     <row r="219" spans="1:9">
-      <c r="A219" s="8">
+      <c r="A219" s="11">
         <v>216</v>
       </c>
-      <c r="B219" s="14"/>
-      <c r="C219" s="17" t="s">
+      <c r="B219" s="17"/>
+      <c r="C219" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D219" s="17" t="s">
+      <c r="D219" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="E219" s="8"/>
-      <c r="F219" s="8"/>
-      <c r="G219" s="9"/>
-      <c r="H219" s="8"/>
-      <c r="I219" s="21"/>
+      <c r="E219" s="11"/>
+      <c r="F219" s="11"/>
+      <c r="G219" s="12"/>
+      <c r="H219" s="11"/>
+      <c r="I219" s="24"/>
     </row>
     <row r="220" spans="1:9">
-      <c r="A220" s="8">
+      <c r="A220" s="11">
         <v>217</v>
       </c>
-      <c r="B220" s="14"/>
-      <c r="C220" s="17" t="s">
+      <c r="B220" s="17"/>
+      <c r="C220" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="D220" s="17" t="s">
+      <c r="D220" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="E220" s="8"/>
-      <c r="F220" s="8"/>
-      <c r="G220" s="9"/>
-      <c r="H220" s="8"/>
-      <c r="I220" s="21"/>
+      <c r="E220" s="11"/>
+      <c r="F220" s="11"/>
+      <c r="G220" s="12"/>
+      <c r="H220" s="11"/>
+      <c r="I220" s="24"/>
     </row>
     <row r="221" spans="1:9">
-      <c r="A221" s="8">
+      <c r="A221" s="11">
         <v>220</v>
       </c>
-      <c r="B221" s="14"/>
-      <c r="C221" s="17"/>
-      <c r="D221" s="17"/>
-      <c r="E221" s="8"/>
-      <c r="F221" s="8"/>
-      <c r="G221" s="9"/>
-      <c r="H221" s="8"/>
-      <c r="I221" s="21"/>
+      <c r="B221" s="17"/>
+      <c r="C221" s="20"/>
+      <c r="D221" s="20"/>
+      <c r="E221" s="11"/>
+      <c r="F221" s="11"/>
+      <c r="G221" s="12"/>
+      <c r="H221" s="11"/>
+      <c r="I221" s="24"/>
     </row>
     <row r="222" spans="1:9">
-      <c r="A222" s="8"/>
-      <c r="B222" s="14"/>
-      <c r="C222" s="17"/>
-      <c r="D222" s="17"/>
-      <c r="E222" s="8"/>
-      <c r="F222" s="8"/>
-      <c r="G222" s="9"/>
-      <c r="H222" s="8"/>
-      <c r="I222" s="21"/>
+      <c r="A222" s="11"/>
+      <c r="B222" s="17"/>
+      <c r="C222" s="20"/>
+      <c r="D222" s="20"/>
+      <c r="E222" s="11"/>
+      <c r="F222" s="11"/>
+      <c r="G222" s="12"/>
+      <c r="H222" s="11"/>
+      <c r="I222" s="24"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I221" etc:filterBottomFollowUsedRange="0">
@@ -6824,1224 +6878,219 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="9.02654867256637" style="3"/>
+    <col min="1" max="2" width="9.02654867256637" style="2"/>
+    <col min="3" max="3" width="12.858407079646" style="2" customWidth="1"/>
+    <col min="4" max="11" width="25.4955752212389" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.02654867256637" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:15">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:15">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:15">
-      <c r="A3"/>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:15">
-      <c r="A4"/>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:15">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:15">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:15">
-      <c r="A7"/>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:15">
-      <c r="A8"/>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:15">
-      <c r="A9"/>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:15">
-      <c r="A10"/>
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:15">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:15">
-      <c r="A12"/>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:15">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:15">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:15">
-      <c r="A15"/>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:15">
-      <c r="A16"/>
-      <c r="B16"/>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:10">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:10">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:10">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:10">
-      <c r="A20"/>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:10">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:10">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:10">
-      <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:10">
-      <c r="A24"/>
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="1:10">
-      <c r="A25"/>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="1:10">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="1:10">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27"/>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="1:10">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28"/>
-      <c r="J28"/>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="1:10">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
-      <c r="I29"/>
-      <c r="J29"/>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="1:10">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="1:10">
-      <c r="A31"/>
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31"/>
-      <c r="H31"/>
-      <c r="I31"/>
-      <c r="J31"/>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="1:10">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="1:10">
-      <c r="A33"/>
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
-      <c r="I33"/>
-      <c r="J33"/>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:10">
-      <c r="A34"/>
-      <c r="B34"/>
-      <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="H34"/>
-      <c r="I34"/>
-      <c r="J34"/>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="1:10">
-      <c r="A35"/>
-      <c r="B35"/>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:10">
-      <c r="A36"/>
-      <c r="B36"/>
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:10">
-      <c r="A37"/>
-      <c r="B37"/>
-      <c r="C37"/>
-      <c r="D37"/>
-      <c r="E37"/>
-      <c r="F37"/>
-      <c r="G37"/>
-      <c r="H37"/>
-      <c r="I37"/>
-      <c r="J37"/>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="1:10">
-      <c r="A38"/>
-      <c r="B38"/>
-      <c r="C38"/>
-      <c r="D38"/>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38"/>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="1:10">
-      <c r="A39"/>
-      <c r="B39"/>
-      <c r="C39"/>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39"/>
-    </row>
-    <row r="40" s="2" customFormat="1" spans="1:10">
-      <c r="A40"/>
-      <c r="B40"/>
-      <c r="C40"/>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40"/>
-      <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40"/>
-    </row>
-    <row r="41" s="2" customFormat="1" spans="1:10">
-      <c r="A41"/>
-      <c r="B41"/>
-      <c r="C41"/>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="G41"/>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="J41"/>
-    </row>
-    <row r="42" s="2" customFormat="1" spans="1:10">
-      <c r="A42"/>
-      <c r="B42"/>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-    </row>
-    <row r="43" s="2" customFormat="1" spans="1:10">
-      <c r="A43"/>
-      <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43"/>
-    </row>
-    <row r="44" s="2" customFormat="1" spans="1:10">
-      <c r="A44"/>
-      <c r="B44"/>
-      <c r="C44"/>
-      <c r="D44"/>
-      <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
-      <c r="I44"/>
-      <c r="J44"/>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="1:10">
-      <c r="A45"/>
-      <c r="B45"/>
-      <c r="C45"/>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-    </row>
-    <row r="46" s="2" customFormat="1" spans="1:10">
-      <c r="A46"/>
-      <c r="B46"/>
-      <c r="C46"/>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46"/>
-    </row>
-    <row r="47" s="2" customFormat="1" spans="1:10">
-      <c r="A47"/>
-      <c r="B47"/>
-      <c r="C47"/>
-      <c r="D47"/>
-      <c r="E47"/>
-      <c r="F47"/>
-      <c r="G47"/>
-      <c r="H47"/>
-      <c r="I47"/>
-      <c r="J47"/>
-    </row>
-    <row r="48" s="2" customFormat="1" spans="1:10">
-      <c r="A48"/>
-      <c r="B48"/>
-      <c r="C48"/>
-      <c r="D48"/>
-      <c r="E48"/>
-      <c r="F48"/>
-      <c r="G48"/>
-      <c r="H48"/>
-      <c r="I48"/>
-      <c r="J48"/>
-    </row>
-    <row r="49" s="2" customFormat="1" spans="1:10">
-      <c r="A49"/>
-      <c r="B49"/>
-      <c r="C49"/>
-      <c r="D49"/>
-      <c r="E49"/>
-      <c r="F49"/>
-      <c r="G49"/>
-      <c r="H49"/>
-      <c r="I49"/>
-      <c r="J49"/>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:10">
-      <c r="A50"/>
-      <c r="B50"/>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
-      <c r="I50"/>
-      <c r="J50"/>
-    </row>
-    <row r="51" s="2" customFormat="1" spans="1:10">
-      <c r="A51"/>
-      <c r="B51"/>
-      <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51"/>
-    </row>
-    <row r="52" s="2" customFormat="1" spans="1:10">
-      <c r="A52"/>
-      <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-    </row>
-    <row r="53" s="2" customFormat="1" spans="1:10">
-      <c r="A53"/>
-      <c r="B53"/>
-      <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-    </row>
-    <row r="54" s="2" customFormat="1" spans="1:10">
-      <c r="A54"/>
-      <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-    </row>
-    <row r="55" s="2" customFormat="1" spans="1:10">
-      <c r="A55"/>
-      <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-    </row>
-    <row r="56" s="2" customFormat="1" spans="1:10">
-      <c r="A56"/>
-      <c r="B56"/>
-      <c r="C56"/>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
-      <c r="I56"/>
-      <c r="J56"/>
-    </row>
-    <row r="57" s="2" customFormat="1" spans="1:10">
-      <c r="A57"/>
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
-      <c r="I57"/>
-      <c r="J57"/>
-    </row>
-    <row r="58" s="2" customFormat="1" spans="1:10">
-      <c r="A58"/>
-      <c r="B58"/>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
-      <c r="H58"/>
-      <c r="I58"/>
-      <c r="J58"/>
-    </row>
-    <row r="59" s="2" customFormat="1" spans="1:10">
-      <c r="A59"/>
-      <c r="B59"/>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59"/>
-    </row>
-    <row r="60" s="2" customFormat="1" spans="1:10">
-      <c r="A60"/>
-      <c r="B60"/>
-      <c r="C60"/>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
-      <c r="H60"/>
-      <c r="I60"/>
-      <c r="J60"/>
-    </row>
-    <row r="61" s="2" customFormat="1" spans="1:10">
-      <c r="A61"/>
-      <c r="B61"/>
-      <c r="C61"/>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
-      <c r="H61"/>
-      <c r="I61"/>
-      <c r="J61"/>
-    </row>
-    <row r="62" s="2" customFormat="1" spans="1:10">
-      <c r="A62"/>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62"/>
-    </row>
-    <row r="63" s="2" customFormat="1" spans="1:10">
-      <c r="A63"/>
-      <c r="B63"/>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63"/>
-      <c r="I63"/>
-      <c r="J63"/>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:10">
-      <c r="A64"/>
-      <c r="B64"/>
-      <c r="C64"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-    </row>
-    <row r="65" s="2" customFormat="1" spans="1:10">
-      <c r="A65"/>
-      <c r="B65"/>
-      <c r="C65"/>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:10">
-      <c r="A66"/>
-      <c r="B66"/>
-      <c r="C66"/>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-    </row>
-    <row r="67" s="2" customFormat="1" spans="1:10">
-      <c r="A67"/>
-      <c r="B67"/>
-      <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-    </row>
-    <row r="68" s="2" customFormat="1" spans="1:10">
-      <c r="A68"/>
-      <c r="B68"/>
-      <c r="C68"/>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:10">
-      <c r="A69"/>
-      <c r="B69"/>
-      <c r="C69"/>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="H69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="1:10">
-      <c r="A70"/>
-      <c r="B70"/>
-      <c r="C70"/>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:10">
-      <c r="A71"/>
-      <c r="B71"/>
-      <c r="C71"/>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71"/>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="1:10">
-      <c r="A72"/>
-      <c r="B72"/>
-      <c r="C72"/>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
-      <c r="G72"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-    </row>
-    <row r="73" s="2" customFormat="1" spans="1:10">
-      <c r="A73"/>
-      <c r="B73"/>
-      <c r="C73"/>
-      <c r="D73"/>
-      <c r="E73"/>
-      <c r="F73"/>
-      <c r="G73"/>
-      <c r="H73"/>
-      <c r="I73"/>
-      <c r="J73"/>
-    </row>
-    <row r="74" s="2" customFormat="1" spans="1:10">
-      <c r="A74"/>
-      <c r="B74"/>
-      <c r="C74"/>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74"/>
-      <c r="G74"/>
-      <c r="H74"/>
-      <c r="I74"/>
-      <c r="J74"/>
-    </row>
-    <row r="75" s="2" customFormat="1" spans="1:10">
-      <c r="A75"/>
-      <c r="B75"/>
-      <c r="C75"/>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
-      <c r="G75"/>
-      <c r="H75"/>
-      <c r="I75"/>
-      <c r="J75"/>
-    </row>
-    <row r="76" s="2" customFormat="1" spans="1:10">
-      <c r="A76"/>
-      <c r="B76"/>
-      <c r="C76"/>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
-      <c r="G76"/>
-      <c r="H76"/>
-      <c r="I76"/>
-      <c r="J76"/>
-    </row>
-    <row r="77" s="2" customFormat="1" spans="1:10">
-      <c r="A77"/>
-      <c r="B77"/>
-      <c r="C77"/>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="G77"/>
-      <c r="H77"/>
-      <c r="I77"/>
-      <c r="J77"/>
-    </row>
-    <row r="78" s="2" customFormat="1" spans="1:10">
-      <c r="A78"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
-      <c r="I78"/>
-      <c r="J78"/>
-    </row>
-    <row r="79" s="2" customFormat="1" spans="1:10">
-      <c r="A79"/>
-      <c r="B79"/>
-      <c r="C79"/>
-      <c r="D79"/>
-      <c r="E79"/>
-      <c r="F79"/>
-      <c r="G79"/>
-      <c r="H79"/>
-      <c r="I79"/>
-      <c r="J79"/>
-    </row>
-    <row r="80" s="2" customFormat="1" spans="1:10">
-      <c r="A80"/>
-      <c r="B80"/>
-      <c r="C80"/>
-      <c r="D80"/>
-      <c r="E80"/>
-      <c r="F80"/>
-      <c r="G80"/>
-      <c r="H80"/>
-      <c r="I80"/>
-      <c r="J80"/>
-    </row>
-    <row r="81" s="2" customFormat="1" spans="1:10">
-      <c r="A81"/>
-      <c r="B81"/>
-      <c r="C81"/>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
-      <c r="G81"/>
-      <c r="H81"/>
-      <c r="I81"/>
-      <c r="J81"/>
-    </row>
-    <row r="82" s="2" customFormat="1" spans="1:10">
-      <c r="A82"/>
-      <c r="B82"/>
-      <c r="C82"/>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
-      <c r="G82"/>
-      <c r="H82"/>
-      <c r="I82"/>
-      <c r="J82"/>
-    </row>
-    <row r="83" s="2" customFormat="1" spans="1:10">
-      <c r="A83"/>
-      <c r="B83"/>
-      <c r="C83"/>
-      <c r="D83"/>
-      <c r="E83"/>
-      <c r="F83"/>
-      <c r="G83"/>
-      <c r="H83"/>
-      <c r="I83"/>
-      <c r="J83"/>
-    </row>
-    <row r="84" s="2" customFormat="1" spans="1:10">
-      <c r="A84"/>
-      <c r="B84"/>
-      <c r="C84"/>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
-      <c r="I84"/>
-      <c r="J84"/>
-    </row>
-    <row r="85" s="2" customFormat="1" spans="1:10">
-      <c r="A85"/>
-      <c r="B85"/>
-      <c r="C85"/>
-      <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
-      <c r="G85"/>
-      <c r="H85"/>
-      <c r="I85"/>
-      <c r="J85"/>
-    </row>
-    <row r="86" s="2" customFormat="1" spans="1:10">
-      <c r="A86"/>
-      <c r="B86"/>
-      <c r="C86"/>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
-      <c r="I86"/>
-      <c r="J86"/>
-    </row>
-    <row r="87" s="2" customFormat="1" spans="1:10">
-      <c r="A87"/>
-      <c r="B87"/>
-      <c r="C87"/>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
-      <c r="I87"/>
-      <c r="J87"/>
-    </row>
-    <row r="88" s="2" customFormat="1" spans="1:10">
-      <c r="A88"/>
-      <c r="B88"/>
-      <c r="C88"/>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88"/>
-      <c r="I88"/>
-      <c r="J88"/>
-    </row>
-    <row r="89" s="2" customFormat="1" spans="1:10">
-      <c r="A89"/>
-      <c r="B89"/>
-      <c r="C89"/>
-      <c r="D89"/>
-      <c r="E89"/>
-      <c r="F89"/>
-      <c r="G89"/>
-      <c r="H89"/>
-      <c r="I89"/>
-      <c r="J89"/>
-    </row>
-    <row r="90" s="2" customFormat="1" spans="1:10">
-      <c r="A90"/>
-      <c r="B90"/>
-      <c r="C90"/>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
-      <c r="G90"/>
-      <c r="H90"/>
-      <c r="I90"/>
-      <c r="J90"/>
-    </row>
-    <row r="91" s="2" customFormat="1" spans="1:10">
-      <c r="A91"/>
-      <c r="B91"/>
-      <c r="C91"/>
-      <c r="D91"/>
-      <c r="E91"/>
-      <c r="F91"/>
-      <c r="G91"/>
-      <c r="H91"/>
-      <c r="I91"/>
-      <c r="J91"/>
-    </row>
-    <row r="92" s="2" customFormat="1" spans="1:10">
-      <c r="A92"/>
-      <c r="B92"/>
-      <c r="C92"/>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92"/>
-      <c r="H92"/>
-      <c r="I92"/>
-      <c r="J92"/>
-    </row>
-    <row r="93" s="2" customFormat="1" spans="1:10">
-      <c r="A93"/>
-      <c r="B93"/>
-      <c r="C93"/>
-      <c r="D93"/>
-      <c r="E93"/>
-      <c r="F93"/>
-      <c r="G93"/>
-      <c r="H93"/>
-      <c r="I93"/>
-      <c r="J93"/>
-    </row>
-    <row r="94" s="2" customFormat="1" spans="1:10">
-      <c r="A94"/>
-      <c r="B94"/>
-      <c r="C94"/>
-      <c r="D94"/>
-      <c r="E94"/>
-      <c r="F94"/>
-      <c r="G94"/>
-      <c r="H94"/>
-      <c r="I94"/>
-      <c r="J94"/>
-    </row>
-    <row r="95" s="2" customFormat="1" spans="1:10">
-      <c r="A95"/>
-      <c r="B95"/>
-      <c r="C95"/>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95"/>
-      <c r="G95"/>
-      <c r="H95"/>
-      <c r="I95"/>
-      <c r="J95"/>
-    </row>
-    <row r="96" s="2" customFormat="1" spans="1:10">
-      <c r="A96"/>
-      <c r="B96"/>
-      <c r="C96"/>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
-      <c r="G96"/>
-      <c r="H96"/>
-      <c r="I96"/>
-      <c r="J96"/>
-    </row>
-    <row r="97" s="2" customFormat="1" spans="1:10">
-      <c r="A97"/>
-      <c r="B97"/>
-      <c r="C97"/>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
-      <c r="G97"/>
-      <c r="H97"/>
-      <c r="I97"/>
-      <c r="J97"/>
-    </row>
-    <row r="98" s="2" customFormat="1" spans="1:10">
-      <c r="A98"/>
-      <c r="B98"/>
-      <c r="C98"/>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
-      <c r="G98"/>
-      <c r="H98"/>
-      <c r="I98"/>
-      <c r="J98"/>
-    </row>
-    <row r="99" s="2" customFormat="1" spans="1:10">
-      <c r="A99"/>
-      <c r="B99"/>
-      <c r="C99"/>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
-      <c r="G99"/>
-      <c r="H99"/>
-      <c r="I99"/>
-      <c r="J99"/>
+      <c r="K1" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6">
+        <v>46233</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6">
+        <v>46237</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Другое/Кино.xlsx
+++ b/Другое/Кино.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="10980" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980"/>
   </bookViews>
   <sheets>
     <sheet name="Кино" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Кино!$A$1:$I$221</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="401">
   <si>
     <t>№</t>
   </si>
@@ -901,31 +901,375 @@
     <t>Пн</t>
   </si>
   <si>
-    <t>Отжимания на отжималка 2по 10</t>
-  </si>
-  <si>
     <t>Рабочий вес 20 кг - 4 подхода по 10 раз</t>
+  </si>
+  <si>
+    <t>Вт</t>
+  </si>
+  <si>
+    <t>Скручивания на коврике 3 по 15</t>
+  </si>
+  <si>
+    <t>Отжимания на отжималках 2 по 10</t>
+  </si>
+  <si>
+    <t>Отжимания на отжималках (10, 12, 12)</t>
+  </si>
+  <si>
+    <t>20 кг - 10 раз
+25 кг - 3 по 10 раз</t>
+  </si>
+  <si>
+    <t>Автор</t>
+  </si>
+  <si>
+    <t>451 градус по Фаренгейту</t>
+  </si>
+  <si>
+    <t>Комментарий</t>
+  </si>
+  <si>
+    <t>Рэй Брэдбери</t>
+  </si>
+  <si>
+    <t>В рамках подготовки к сочинению (11 класс)</t>
+  </si>
+  <si>
+    <t>Дуxless</t>
+  </si>
+  <si>
+    <t>Сергей Минаев</t>
+  </si>
+  <si>
+    <t>Первая книга, которую я прочитал по своей воле и перечитал в армии</t>
+  </si>
+  <si>
+    <t>Media Sapiens 1</t>
+  </si>
+  <si>
+    <t>Media Sapiens 2</t>
+  </si>
+  <si>
+    <t>Первый раз прочитал в армии, а через год зачем-то перечитал</t>
+  </si>
+  <si>
+    <t>Дата 3-го прочтения</t>
+  </si>
+  <si>
+    <t>Дата 2-го прочтения</t>
+  </si>
+  <si>
+    <t>Дата 1-го прочтения</t>
+  </si>
+  <si>
+    <t>РАБ</t>
+  </si>
+  <si>
+    <t>Прочитал в армии</t>
+  </si>
+  <si>
+    <t>The Телки</t>
+  </si>
+  <si>
+    <t>The Телки 2</t>
+  </si>
+  <si>
+    <t>Жанр</t>
+  </si>
+  <si>
+    <t>Роман</t>
+  </si>
+  <si>
+    <t>Селфи</t>
+  </si>
+  <si>
+    <t>69 психотрюков</t>
+  </si>
+  <si>
+    <t>Игорь Рызов</t>
+  </si>
+  <si>
+    <t>Психология</t>
+  </si>
+  <si>
+    <t>Прочитал в течение года после армии</t>
+  </si>
+  <si>
+    <t>Три товарища</t>
+  </si>
+  <si>
+    <t>Эрих Мария Ремарк</t>
+  </si>
+  <si>
+    <t>Стремись услышать нет</t>
+  </si>
+  <si>
+    <t>Ричард Фентон</t>
+  </si>
+  <si>
+    <t>Саморазвитие</t>
+  </si>
+  <si>
+    <t>Договориться можно обо всем</t>
+  </si>
+  <si>
+    <t>Гэвин Кеннеди</t>
+  </si>
+  <si>
+    <t>Бизнес без MBA</t>
+  </si>
+  <si>
+    <t>Тинькофф</t>
+  </si>
+  <si>
+    <t>Бизнес</t>
+  </si>
+  <si>
+    <t>Ларри Кинг</t>
+  </si>
+  <si>
+    <t>Как разговаривать с кем угодно, когда угодно и где угодно</t>
+  </si>
+  <si>
+    <t>Любовь живет 3 года</t>
+  </si>
+  <si>
+    <t>Фредерик Бегбедер</t>
+  </si>
+  <si>
+    <t>Джером К. Джером</t>
+  </si>
+  <si>
+    <t>Трое в лодке, не считая собаки</t>
+  </si>
+  <si>
+    <t>Юмористическая повесть</t>
+  </si>
+  <si>
+    <t>Тонкое искусство пофигизма</t>
+  </si>
+  <si>
+    <t>Марк Мэнсон</t>
+  </si>
+  <si>
+    <t>Я вижу о чем вы думаете</t>
+  </si>
+  <si>
+    <t>Джо Наварро</t>
+  </si>
+  <si>
+    <t>Клэр Пули</t>
+  </si>
+  <si>
+    <t>Люди с платформы № 5</t>
+  </si>
+  <si>
+    <t>Джордж Сэмюэль Клейсон</t>
+  </si>
+  <si>
+    <t>Самый богатый человек в Вавилоне</t>
+  </si>
+  <si>
+    <t>Прикладное лоховедение</t>
+  </si>
+  <si>
+    <t>Егор Белогородский</t>
+  </si>
+  <si>
+    <t>Идиот</t>
+  </si>
+  <si>
+    <t>Федор Достаевский</t>
+  </si>
+  <si>
+    <t>Классика</t>
+  </si>
+  <si>
+    <t>Салли Руни</t>
+  </si>
+  <si>
+    <t>Прекрасный мир, где же ты</t>
+  </si>
+  <si>
+    <t>2023-2024</t>
+  </si>
+  <si>
+    <t>Лягушка, слон и брокколи</t>
+  </si>
+  <si>
+    <t>Алексей Марков</t>
+  </si>
+  <si>
+    <t>Достаточно легко читается и дает неплохой мотивационный толчок</t>
+  </si>
+  <si>
+    <t>99 франков</t>
+  </si>
+  <si>
+    <t>Сложно читалась, осилил ее с 3 раза</t>
+  </si>
+  <si>
+    <t>Перечитыва в армии</t>
+  </si>
+  <si>
+    <t>Москва, я не люблю тебя</t>
+  </si>
+  <si>
+    <t>11/22/63</t>
+  </si>
+  <si>
+    <t>Стивен Кинг</t>
+  </si>
+  <si>
+    <t>Фантастический роман</t>
+  </si>
+  <si>
+    <t>Очень понравилось, вайб америки 60-ых + интересный сюжет</t>
+  </si>
+  <si>
+    <t>Майк Омер</t>
+  </si>
+  <si>
+    <t>Внутри убийцы</t>
+  </si>
+  <si>
+    <t>Детектив</t>
+  </si>
+  <si>
+    <t>Крепкий детектив, но не показался каким-то уж больно особенным</t>
+  </si>
+  <si>
+    <t>Зелёный свет</t>
+  </si>
+  <si>
+    <t>Автобиография</t>
+  </si>
+  <si>
+    <t>Очень понравилось, приятно читается, теплая атмосфера, хорошо успокаивает и заряжает</t>
+  </si>
+  <si>
+    <t>Джон Стейнбек</t>
+  </si>
+  <si>
+    <t>О мышах и людях</t>
+  </si>
+  <si>
+    <t>В произведении 2 новеллы. Первая в меня попала, а вторая не очень</t>
+  </si>
+  <si>
+    <t>Ничего не помню, вроде роман был слабоват</t>
+  </si>
+  <si>
+    <t>Ирвин Шоу</t>
+  </si>
+  <si>
+    <t>Богач, бедняк</t>
+  </si>
+  <si>
+    <t>Sapiens. Краткая история человечества</t>
+  </si>
+  <si>
+    <t>Юваль Ной Харари</t>
+  </si>
+  <si>
+    <t>Научпоп</t>
+  </si>
+  <si>
+    <t>Роберт Льюис Стивенсон</t>
+  </si>
+  <si>
+    <t>Клуб самоубийц</t>
+  </si>
+  <si>
+    <t>Триумфальная арка</t>
+  </si>
+  <si>
+    <t>На западном фронте без перемен</t>
+  </si>
+  <si>
+    <t>Бремя страстей человеческих</t>
+  </si>
+  <si>
+    <t>Уильям Сомерсет Моэм</t>
+  </si>
+  <si>
+    <t>Падение Эдварда Барнарда</t>
+  </si>
+  <si>
+    <t>Роман на крыше</t>
+  </si>
+  <si>
+    <t>Пелам Гренвилл Вудхаус</t>
+  </si>
+  <si>
+    <t>Фантастика</t>
+  </si>
+  <si>
+    <t>Стрелок</t>
+  </si>
+  <si>
+    <t>Извлечение троих</t>
+  </si>
+  <si>
+    <t>Бесплодные земли</t>
+  </si>
+  <si>
+    <t>Колдун и кристалл</t>
+  </si>
+  <si>
+    <t>Ветер сквозь замочную скважину</t>
+  </si>
+  <si>
+    <t>Похороните меня за плинтусом</t>
+  </si>
+  <si>
+    <t>Павел Санаев</t>
+  </si>
+  <si>
+    <t>Автобиографическая повесть</t>
+  </si>
+  <si>
+    <t>Не особо запало в душу</t>
+  </si>
+  <si>
+    <t>Волки Кальи</t>
+  </si>
+  <si>
+    <t>Песнь Сюзанны</t>
+  </si>
+  <si>
+    <t>Игра Джералда</t>
+  </si>
+  <si>
+    <t>Ужасы</t>
+  </si>
+  <si>
+    <t>Мизери</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="8">
-    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="dd\.mmm"/>
-    <numFmt numFmtId="181" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="182" formatCode="mmm\.yy"/>
-    <numFmt numFmtId="183" formatCode="0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="168" formatCode="dd\.mmm"/>
+    <numFmt numFmtId="169" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="170" formatCode="mmm\.yy"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -948,158 +1292,24 @@
       <charset val="204"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="6" tint="-0.499984740745262"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1108,19 +1318,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.35"/>
+        <fgColor theme="1" tint="0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="-0.5"/>
+        <fgColor theme="3" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.349986266670736"/>
+        <fgColor theme="1" tint="0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1132,192 +1342,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1327,300 +1363,58 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.25"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.25"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.25"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.25"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="1" tint="0.349986266670736"/>
+        <color theme="1" tint="0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color theme="1" tint="0.349986266670736"/>
+        <color theme="1" tint="0.34998626667073579"/>
       </right>
       <top style="thin">
-        <color theme="1" tint="0.349986266670736"/>
+        <color theme="1" tint="0.34998626667073579"/>
       </top>
       <bottom style="thin">
-        <color theme="1" tint="0.349986266670736"/>
+        <color theme="1" tint="0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="1" tint="0.349986266670736"/>
+        <color theme="1" tint="0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color theme="1" tint="0.349986266670736"/>
+        <color theme="1" tint="0.34998626667073579"/>
       </right>
       <top style="thin">
-        <color theme="1" tint="0.349986266670736"/>
+        <color theme="1" tint="0.34998626667073579"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1629,7 +1423,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1639,115 +1433,115 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1761,9 +1555,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00BAE18F"/>
-      <color rgb="00DFF1CB"/>
-      <color rgb="00F99D41"/>
+      <color rgb="FFBAE18F"/>
+      <color rgb="FFDFF1CB"/>
+      <color rgb="FFF99D41"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2055,27 +1849,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I222"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.14159292035398" style="9"/>
-    <col min="2" max="2" width="24.858407079646" style="9" customWidth="1"/>
-    <col min="3" max="3" width="22.141592920354" style="9" customWidth="1"/>
-    <col min="4" max="4" width="43.283185840708" style="9" customWidth="1"/>
-    <col min="5" max="5" width="11.4247787610619" style="9" customWidth="1"/>
-    <col min="6" max="6" width="16.4247787610619" style="9" customWidth="1"/>
-    <col min="7" max="8" width="14.858407079646" style="9" customWidth="1"/>
-    <col min="9" max="9" width="16.283185840708" style="9" customWidth="1"/>
-    <col min="10" max="16384" width="9.14159292035398" style="9"/>
+    <col min="1" max="1" width="9.140625" style="9"/>
+    <col min="2" max="2" width="24.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="43.28515625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="9" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" style="9" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2536,7 +2330,7 @@
       <c r="H19" s="11"/>
       <c r="I19" s="14"/>
     </row>
-    <row r="20" ht="27" spans="1:9">
+    <row r="20" spans="1:9" ht="29.25">
       <c r="A20" s="11">
         <v>36</v>
       </c>
@@ -2553,7 +2347,7 @@
         <v>1972</v>
       </c>
       <c r="F20" s="11">
-        <v>8.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>15</v>
@@ -2588,7 +2382,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="14"/>
     </row>
-    <row r="22" ht="27" spans="1:9">
+    <row r="22" spans="1:9" ht="29.25">
       <c r="A22" s="11">
         <v>37</v>
       </c>
@@ -2718,7 +2512,7 @@
         <v>1979</v>
       </c>
       <c r="F27" s="11">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="20"/>
@@ -2835,7 +2629,7 @@
         <v>1983</v>
       </c>
       <c r="F32" s="11">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="G32" s="12"/>
       <c r="H32" s="20"/>
@@ -3150,7 +2944,7 @@
         <v>1994</v>
       </c>
       <c r="F45" s="11">
-        <v>8.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>15</v>
@@ -3206,7 +3000,7 @@
         <v>1995</v>
       </c>
       <c r="F47" s="11">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>15</v>
@@ -3302,7 +3096,7 @@
         <v>1997</v>
       </c>
       <c r="F51" s="11">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>15</v>
@@ -3446,7 +3240,7 @@
         <v>1999</v>
       </c>
       <c r="F57" s="11">
-        <v>8.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>15</v>
@@ -3629,7 +3423,7 @@
       <c r="H64" s="20"/>
       <c r="I64" s="20"/>
     </row>
-    <row r="65" ht="27" spans="1:9">
+    <row r="65" spans="1:9" ht="42.75">
       <c r="A65" s="11">
         <v>31</v>
       </c>
@@ -3892,7 +3686,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="76" ht="40.5" spans="1:9">
+    <row r="76" spans="1:9" ht="57">
       <c r="A76" s="11">
         <v>30</v>
       </c>
@@ -4050,7 +3844,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" ht="29.25">
       <c r="A82" s="11">
         <v>62</v>
       </c>
@@ -4273,7 +4067,7 @@
         <v>2010</v>
       </c>
       <c r="F90" s="11">
-        <v>8.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>15</v>
@@ -4363,7 +4157,7 @@
         <v>2010</v>
       </c>
       <c r="F94" s="11">
-        <v>8.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G94" s="12" t="s">
         <v>15</v>
@@ -4482,7 +4276,7 @@
         <v>2012</v>
       </c>
       <c r="F99" s="11">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="G99" s="12" t="s">
         <v>15</v>
@@ -4523,7 +4317,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="101" ht="27" spans="1:9">
+    <row r="101" spans="1:9" ht="42.75">
       <c r="A101" s="11">
         <v>32</v>
       </c>
@@ -4646,7 +4440,7 @@
         <v>2014</v>
       </c>
       <c r="F105" s="11">
-        <v>8.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>15</v>
@@ -4658,7 +4452,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="106" ht="27" spans="1:9">
+    <row r="106" spans="1:9" ht="28.5">
       <c r="A106" s="11">
         <v>128</v>
       </c>
@@ -4871,7 +4665,7 @@
       <c r="H114" s="20"/>
       <c r="I114" s="20"/>
     </row>
-    <row r="115" ht="27" spans="1:9">
+    <row r="115" spans="1:9" ht="28.5">
       <c r="A115" s="11">
         <v>34</v>
       </c>
@@ -4938,7 +4732,7 @@
         <v>2019</v>
       </c>
       <c r="F117" s="11">
-        <v>8.7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>15</v>
@@ -5136,7 +4930,7 @@
         <v>44713</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" ht="29.25">
       <c r="A126" s="11">
         <v>122</v>
       </c>
@@ -5157,7 +4951,7 @@
       <c r="H126" s="11"/>
       <c r="I126" s="20"/>
     </row>
-    <row r="127" ht="27" spans="1:9">
+    <row r="127" spans="1:9" ht="42.75">
       <c r="A127" s="11">
         <v>35</v>
       </c>
@@ -5249,7 +5043,7 @@
         <v>2024</v>
       </c>
       <c r="F130" s="11">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="G130" s="12"/>
       <c r="H130" s="20"/>
@@ -6834,10 +6628,7 @@
       <c r="I222" s="24"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I221" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:I221">
-      <sortCondition ref="E1"/>
-    </sortState>
+  <autoFilter ref="A1:I221">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A2:I222">
@@ -6845,49 +6636,1831 @@
       <formula>$G2="Просмотрен"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.708661417322835" right="0.708661417322835" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" horizontalDpi="180" verticalDpi="180"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H101"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="33.7109375" style="9" customWidth="1"/>
+    <col min="3" max="4" width="27.140625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="54.140625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" style="9" customWidth="1"/>
+    <col min="7" max="8" width="12.85546875" style="9" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="35" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>310</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="35" customFormat="1" ht="30" customHeight="1">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>298</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="F2" s="34">
+        <v>2015</v>
+      </c>
+      <c r="G2" s="34">
+        <v>2022</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="35" customFormat="1" ht="30" customHeight="1">
+      <c r="A3" s="33">
+        <v>2</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>355</v>
+      </c>
+      <c r="F3" s="33">
+        <v>2016</v>
+      </c>
+      <c r="G3" s="41">
+        <v>2022</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="35" customFormat="1" ht="30" customHeight="1">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>371</v>
+      </c>
+      <c r="F4" s="33">
+        <v>2016</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" customHeight="1">
+      <c r="A5" s="33">
+        <v>4</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="F5" s="33">
+        <v>2016</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30" customHeight="1">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>300</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="F6" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G6" s="33">
+        <v>2023</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" customHeight="1">
+      <c r="A7" s="33">
+        <v>6</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="F7" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G7" s="33">
+        <v>2023</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1">
+      <c r="A8" s="34">
+        <v>7</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="F8" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1">
+      <c r="A9" s="33">
+        <v>8</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="F9" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1">
+      <c r="A10" s="34">
+        <v>9</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="F10" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="30" customHeight="1">
+      <c r="A11" s="33">
+        <v>10</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="F11" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30" customHeight="1">
+      <c r="A12" s="34">
+        <v>11</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>315</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="F12" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" customHeight="1">
+      <c r="A13" s="33">
+        <v>12</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="F13" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" customHeight="1">
+      <c r="A14" s="34">
+        <v>13</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>322</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="F14" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="30" customHeight="1">
+      <c r="A15" s="33">
+        <v>14</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>324</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="F15" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30" customHeight="1">
+      <c r="A16" s="34">
+        <v>15</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>328</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="D16" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="F16" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G16" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30" customHeight="1">
+      <c r="A17" s="33">
+        <v>16</v>
+      </c>
+      <c r="B17" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>330</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F17" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30" customHeight="1">
+      <c r="A18" s="34">
+        <v>17</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>333</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F18" s="33">
+        <v>2022</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30" customHeight="1">
+      <c r="A19" s="33">
+        <v>18</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>334</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F19" s="33">
+        <v>2023</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="30" customHeight="1">
+      <c r="A20" s="34">
+        <v>19</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="E20" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F20" s="33">
+        <v>2023</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="30" customHeight="1">
+      <c r="A21" s="33">
+        <v>20</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F21" s="33">
+        <v>2023</v>
+      </c>
+      <c r="G21" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" customHeight="1">
+      <c r="A22" s="34">
+        <v>21</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>348</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>347</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F22" s="33">
+        <v>2023</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="30" customHeight="1">
+      <c r="A23" s="33">
+        <v>22</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>341</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F23" s="33">
+        <v>2023</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="30" customHeight="1">
+      <c r="A24" s="34">
+        <v>23</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="E24" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F24" s="33">
+        <v>2023</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="30" customHeight="1">
+      <c r="A25" s="33">
+        <v>24</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="F25" s="33">
+        <v>2023</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1">
+      <c r="A26" s="34">
+        <v>25</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="30" customHeight="1">
+      <c r="A27" s="33">
+        <v>26</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>353</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="G27" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="30" customHeight="1">
+      <c r="A28" s="34">
+        <v>27</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>395</v>
+      </c>
+      <c r="F28" s="41" t="s">
+        <v>349</v>
+      </c>
+      <c r="G28" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="30" customHeight="1">
+      <c r="A29" s="33">
+        <v>28</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="F29" s="33">
+        <v>2024</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="30" customHeight="1">
+      <c r="A30" s="34">
+        <v>29</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>364</v>
+      </c>
+      <c r="F30" s="33">
+        <v>2025</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="30" customHeight="1">
+      <c r="A31" s="44">
+        <v>30</v>
+      </c>
+      <c r="B31" s="45" t="s">
+        <v>365</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="E31" s="46" t="s">
+        <v>367</v>
+      </c>
+      <c r="F31" s="47">
+        <v>2025</v>
+      </c>
+      <c r="G31" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="30" customHeight="1">
+      <c r="A32" s="33">
+        <v>31</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="F32" s="33">
+        <v>2026</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="30" customHeight="1">
+      <c r="A33" s="33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>373</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>372</v>
+      </c>
+      <c r="D33" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E33" s="38"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+    </row>
+    <row r="34" spans="1:8" ht="30" customHeight="1">
+      <c r="A34" s="33">
+        <v>33</v>
+      </c>
+      <c r="B34" s="43" t="s">
+        <v>374</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>375</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>376</v>
+      </c>
+      <c r="E34" s="38"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+    </row>
+    <row r="35" spans="1:8" ht="30" customHeight="1">
+      <c r="A35" s="33">
+        <v>34</v>
+      </c>
+      <c r="B35" s="42" t="s">
+        <v>378</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>377</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E35" s="37"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+    </row>
+    <row r="36" spans="1:8" ht="30" customHeight="1">
+      <c r="A36" s="33">
+        <v>35</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>318</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+    </row>
+    <row r="37" spans="1:8" ht="30" customHeight="1">
+      <c r="A37" s="33">
+        <v>36</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>318</v>
+      </c>
+      <c r="D37" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+    </row>
+    <row r="38" spans="1:8" ht="30" customHeight="1">
+      <c r="A38" s="33">
+        <v>37</v>
+      </c>
+      <c r="B38" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="D38" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+    </row>
+    <row r="39" spans="1:8" ht="30" customHeight="1">
+      <c r="A39" s="33">
+        <v>38</v>
+      </c>
+      <c r="B39" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="D39" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+    </row>
+    <row r="40" spans="1:8" ht="30" customHeight="1">
+      <c r="A40" s="33">
+        <v>39</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>384</v>
+      </c>
+      <c r="C40" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="D40" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+    </row>
+    <row r="41" spans="1:8" ht="30" customHeight="1">
+      <c r="A41" s="33">
+        <v>40</v>
+      </c>
+      <c r="B41" s="42" t="s">
+        <v>387</v>
+      </c>
+      <c r="C41" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D41" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+    </row>
+    <row r="42" spans="1:8" ht="30" customHeight="1">
+      <c r="A42" s="33">
+        <v>41</v>
+      </c>
+      <c r="B42" s="42" t="s">
+        <v>388</v>
+      </c>
+      <c r="C42" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D42" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+    </row>
+    <row r="43" spans="1:8" ht="30" customHeight="1">
+      <c r="A43" s="33">
+        <v>42</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>389</v>
+      </c>
+      <c r="C43" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D43" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+    </row>
+    <row r="44" spans="1:8" ht="30" customHeight="1">
+      <c r="A44" s="33">
+        <v>43</v>
+      </c>
+      <c r="B44" s="42" t="s">
+        <v>390</v>
+      </c>
+      <c r="C44" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D44" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+    </row>
+    <row r="45" spans="1:8" ht="30" customHeight="1">
+      <c r="A45" s="33">
+        <v>44</v>
+      </c>
+      <c r="B45" s="42" t="s">
+        <v>391</v>
+      </c>
+      <c r="C45" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D45" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+    </row>
+    <row r="46" spans="1:8" ht="30" customHeight="1">
+      <c r="A46" s="33">
+        <v>45</v>
+      </c>
+      <c r="B46" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="C46" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D46" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+    </row>
+    <row r="47" spans="1:8" ht="30" customHeight="1">
+      <c r="A47" s="33">
+        <v>46</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>397</v>
+      </c>
+      <c r="C47" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D47" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+    </row>
+    <row r="48" spans="1:8" ht="30" customHeight="1">
+      <c r="A48" s="33">
+        <v>47</v>
+      </c>
+      <c r="B48" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="C48" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D48" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="1:8" ht="30" customHeight="1">
+      <c r="A49" s="33">
+        <v>48</v>
+      </c>
+      <c r="B49" s="42" t="s">
+        <v>398</v>
+      </c>
+      <c r="C49" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D49" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+    </row>
+    <row r="50" spans="1:8" ht="30" customHeight="1">
+      <c r="A50" s="33">
+        <v>49</v>
+      </c>
+      <c r="B50" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D50" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+    </row>
+    <row r="51" spans="1:8" ht="30" customHeight="1">
+      <c r="A51" s="33">
+        <v>50</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>400</v>
+      </c>
+      <c r="C51" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D51" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+    </row>
+    <row r="52" spans="1:8" ht="30" customHeight="1">
+      <c r="A52" s="33">
+        <v>51</v>
+      </c>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+    </row>
+    <row r="53" spans="1:8" ht="30" customHeight="1">
+      <c r="A53" s="33">
+        <v>52</v>
+      </c>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+    </row>
+    <row r="54" spans="1:8" ht="30" customHeight="1">
+      <c r="A54" s="33">
+        <v>53</v>
+      </c>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+    </row>
+    <row r="55" spans="1:8" ht="30" customHeight="1">
+      <c r="A55" s="33">
+        <v>54</v>
+      </c>
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+    </row>
+    <row r="56" spans="1:8" ht="30" customHeight="1">
+      <c r="A56" s="33">
+        <v>55</v>
+      </c>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+    </row>
+    <row r="57" spans="1:8" ht="30" customHeight="1">
+      <c r="A57" s="33">
+        <v>56</v>
+      </c>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+    </row>
+    <row r="58" spans="1:8" ht="30" customHeight="1">
+      <c r="A58" s="33">
+        <v>57</v>
+      </c>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+    </row>
+    <row r="59" spans="1:8" ht="30" customHeight="1">
+      <c r="A59" s="33">
+        <v>58</v>
+      </c>
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+    </row>
+    <row r="60" spans="1:8" ht="30" customHeight="1">
+      <c r="A60" s="33">
+        <v>59</v>
+      </c>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+    </row>
+    <row r="61" spans="1:8" ht="30" customHeight="1">
+      <c r="A61" s="33">
+        <v>60</v>
+      </c>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+    </row>
+    <row r="62" spans="1:8" ht="30" customHeight="1">
+      <c r="A62" s="33">
+        <v>61</v>
+      </c>
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
+    </row>
+    <row r="63" spans="1:8" ht="30" customHeight="1">
+      <c r="A63" s="33">
+        <v>62</v>
+      </c>
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63"/>
+    </row>
+    <row r="64" spans="1:8" ht="30" customHeight="1">
+      <c r="A64" s="33">
+        <v>63</v>
+      </c>
+      <c r="B64"/>
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
+    </row>
+    <row r="65" spans="1:8" ht="30" customHeight="1">
+      <c r="A65" s="33">
+        <v>64</v>
+      </c>
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+    </row>
+    <row r="66" spans="1:8" ht="30" customHeight="1">
+      <c r="A66" s="33">
+        <v>65</v>
+      </c>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="1:8" ht="30" customHeight="1">
+      <c r="A67" s="33">
+        <v>66</v>
+      </c>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+    </row>
+    <row r="68" spans="1:8" ht="30" customHeight="1">
+      <c r="A68" s="33">
+        <v>67</v>
+      </c>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
+    </row>
+    <row r="69" spans="1:8" ht="30" customHeight="1">
+      <c r="A69" s="33">
+        <v>68</v>
+      </c>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+    </row>
+    <row r="70" spans="1:8" ht="30" customHeight="1">
+      <c r="A70" s="33">
+        <v>69</v>
+      </c>
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
+    </row>
+    <row r="71" spans="1:8" ht="30" customHeight="1">
+      <c r="A71" s="33">
+        <v>70</v>
+      </c>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+    </row>
+    <row r="72" spans="1:8" ht="30" customHeight="1">
+      <c r="A72" s="33">
+        <v>71</v>
+      </c>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72"/>
+    </row>
+    <row r="73" spans="1:8" ht="30" customHeight="1">
+      <c r="A73" s="33">
+        <v>72</v>
+      </c>
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73"/>
+      <c r="G73"/>
+      <c r="H73"/>
+    </row>
+    <row r="74" spans="1:8" ht="30" customHeight="1">
+      <c r="A74" s="33">
+        <v>73</v>
+      </c>
+      <c r="B74"/>
+      <c r="C74"/>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74"/>
+      <c r="G74"/>
+      <c r="H74"/>
+    </row>
+    <row r="75" spans="1:8" ht="30" customHeight="1">
+      <c r="A75" s="33">
+        <v>74</v>
+      </c>
+      <c r="B75"/>
+      <c r="C75"/>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="H75"/>
+    </row>
+    <row r="76" spans="1:8" ht="30" customHeight="1">
+      <c r="A76" s="33">
+        <v>75</v>
+      </c>
+      <c r="B76"/>
+      <c r="C76"/>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
+      <c r="G76"/>
+      <c r="H76"/>
+    </row>
+    <row r="77" spans="1:8" ht="30" customHeight="1">
+      <c r="A77" s="33">
+        <v>76</v>
+      </c>
+      <c r="B77"/>
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
+    </row>
+    <row r="78" spans="1:8" ht="30" customHeight="1">
+      <c r="A78" s="33">
+        <v>77</v>
+      </c>
+      <c r="B78"/>
+      <c r="C78"/>
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78"/>
+    </row>
+    <row r="79" spans="1:8" ht="30" customHeight="1">
+      <c r="A79" s="33">
+        <v>78</v>
+      </c>
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79"/>
+      <c r="G79"/>
+      <c r="H79"/>
+    </row>
+    <row r="80" spans="1:8" ht="30" customHeight="1">
+      <c r="A80" s="33">
+        <v>79</v>
+      </c>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80"/>
+      <c r="G80"/>
+      <c r="H80"/>
+    </row>
+    <row r="81" spans="1:8" ht="30" customHeight="1">
+      <c r="A81" s="33">
+        <v>80</v>
+      </c>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
+    </row>
+    <row r="82" spans="1:8" ht="30" customHeight="1">
+      <c r="A82" s="33">
+        <v>81</v>
+      </c>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+    </row>
+    <row r="83" spans="1:8" ht="30" customHeight="1">
+      <c r="A83" s="33">
+        <v>82</v>
+      </c>
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+    </row>
+    <row r="84" spans="1:8" ht="30" customHeight="1">
+      <c r="A84" s="33">
+        <v>83</v>
+      </c>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
+    </row>
+    <row r="85" spans="1:8" ht="30" customHeight="1">
+      <c r="A85" s="33">
+        <v>84</v>
+      </c>
+      <c r="B85"/>
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85"/>
+    </row>
+    <row r="86" spans="1:8" ht="30" customHeight="1">
+      <c r="A86" s="33">
+        <v>85</v>
+      </c>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+    </row>
+    <row r="87" spans="1:8" ht="30" customHeight="1">
+      <c r="A87" s="33">
+        <v>86</v>
+      </c>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+    </row>
+    <row r="88" spans="1:8" ht="30" customHeight="1">
+      <c r="A88" s="33">
+        <v>87</v>
+      </c>
+      <c r="B88"/>
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+    </row>
+    <row r="89" spans="1:8" ht="30" customHeight="1">
+      <c r="A89" s="33">
+        <v>88</v>
+      </c>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="H89"/>
+    </row>
+    <row r="90" spans="1:8" ht="30" customHeight="1">
+      <c r="A90" s="33">
+        <v>89</v>
+      </c>
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="H90"/>
+    </row>
+    <row r="91" spans="1:8" ht="30" customHeight="1">
+      <c r="A91" s="33">
+        <v>90</v>
+      </c>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
+    </row>
+    <row r="92" spans="1:8" ht="30" customHeight="1">
+      <c r="A92" s="33">
+        <v>91</v>
+      </c>
+      <c r="B92"/>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="H92"/>
+    </row>
+    <row r="93" spans="1:8" ht="30" customHeight="1">
+      <c r="A93" s="33">
+        <v>92</v>
+      </c>
+      <c r="B93"/>
+      <c r="C93"/>
+      <c r="D93"/>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="G93"/>
+      <c r="H93"/>
+    </row>
+    <row r="94" spans="1:8" ht="30" customHeight="1">
+      <c r="A94" s="33">
+        <v>93</v>
+      </c>
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94"/>
+    </row>
+    <row r="95" spans="1:8" ht="30" customHeight="1">
+      <c r="A95" s="33">
+        <v>94</v>
+      </c>
+      <c r="B95"/>
+      <c r="C95"/>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95"/>
+      <c r="G95"/>
+      <c r="H95"/>
+    </row>
+    <row r="96" spans="1:8" ht="30" customHeight="1">
+      <c r="A96" s="33">
+        <v>95</v>
+      </c>
+      <c r="B96"/>
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96"/>
+      <c r="G96"/>
+      <c r="H96"/>
+    </row>
+    <row r="97" spans="1:8" ht="30" customHeight="1">
+      <c r="A97" s="33">
+        <v>96</v>
+      </c>
+      <c r="B97"/>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+      <c r="H97"/>
+    </row>
+    <row r="98" spans="1:8" ht="30" customHeight="1">
+      <c r="A98" s="33">
+        <v>97</v>
+      </c>
+      <c r="B98"/>
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98"/>
+      <c r="G98"/>
+      <c r="H98"/>
+    </row>
+    <row r="99" spans="1:8" ht="30" customHeight="1">
+      <c r="A99" s="33">
+        <v>98</v>
+      </c>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+    </row>
+    <row r="100" spans="1:8" ht="30" customHeight="1">
+      <c r="A100" s="33">
+        <v>99</v>
+      </c>
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="H100"/>
+    </row>
+    <row r="101" spans="1:8" ht="30" customHeight="1">
+      <c r="A101" s="33">
+        <v>100</v>
+      </c>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C11" r:id="rId1" display="https://yandex.ru/search/?srm=1&amp;text=%D0%AD%D1%80%D0%B8%D1%85%20%D0%9C%D0%B0%D1%80%D0%B8%D1%8F%20%D0%A0%D0%B5%D0%BC%D0%B0%D1%80%D0%BA&amp;lr=14&amp;clid=2270455&amp;win=687&amp;primary_reqid=1786517055526639-14999433768309566645-balancer-l7leveler-kubr-yp-klg-171-BAL&amp;noreask=1&amp;ento=0oCghydXcyMzA3MhgCKglydXcyMzEzNDdqF9Ci0YDQuCDRgtC-0LLQsNGA0LjRidCwcgrQkNCy0YLQvtGAyYrrdg"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="9.02654867256637" style="2"/>
-    <col min="3" max="3" width="12.858407079646" style="2" customWidth="1"/>
-    <col min="4" max="11" width="25.4955752212389" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9.02654867256637" style="2"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="11.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="2" customWidth="1"/>
+    <col min="4" max="11" width="25.42578125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6926,7 +8499,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="2" spans="1:15" ht="30" customHeight="1">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -6949,7 +8522,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="3" spans="1:15" ht="30" customHeight="1">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -6963,31 +8536,43 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>286</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>287</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="4" spans="1:15" ht="30" customHeight="1">
       <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="B4" s="32">
+        <v>46245</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>288</v>
+      </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="G4" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>291</v>
+      </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="5" spans="1:15" ht="30" customHeight="1">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -7002,7 +8587,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="6" spans="1:15" ht="30" customHeight="1">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -7017,7 +8602,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="7" spans="1:15" ht="30" customHeight="1">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -7032,7 +8617,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="8" spans="1:15" ht="30" customHeight="1">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -7047,7 +8632,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="9" spans="1:15" ht="30" customHeight="1">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -7062,7 +8647,7 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="10" spans="1:15" ht="30" customHeight="1">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -7077,7 +8662,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" s="2" customFormat="1" ht="30" customHeight="1" spans="1:15">
+    <row r="11" spans="1:15" ht="30" customHeight="1">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -7094,6 +8679,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>